--- a/calibrations/miscanthus/data/biomass_observation/Miscanthus_Observation_20230529_with_comments.xlsx
+++ b/calibrations/miscanthus/data/biomass_observation/Miscanthus_Observation_20230529_with_comments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ximinpiao/Documents/GitHub/biomass-crops-marginal-land/calibrations/miscanthus/data/biomass_observation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{85AE227B-A259-8B4D-B538-51893187A2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D273BF-FF85-7943-B6B6-0D351D75DBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25620" yWindow="-7340" windowWidth="25620" windowHeight="28200" xr2:uid="{AEFCA9E3-6450-054E-A05D-26B2238FE22C}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16060" xr2:uid="{AEFCA9E3-6450-054E-A05D-26B2238FE22C}"/>
   </bookViews>
   <sheets>
     <sheet name="Miscanthus_Observation_20230529" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -320,14 +320,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -509,7 +503,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,9 +692,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1146,5212 +1168,5212 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
+    <row r="2" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
         <v>-88.85</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>41.85</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>13.929</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="4">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4">
         <v>2004</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="4">
         <v>2002</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="1">
-        <v>4</v>
-      </c>
-      <c r="K2">
+      <c r="J2" s="4">
+        <v>4</v>
+      </c>
+      <c r="K2" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N2">
-        <v>4</v>
-      </c>
-      <c r="O2">
+      <c r="N2" s="4">
+        <v>4</v>
+      </c>
+      <c r="O2" s="4">
         <v>15</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="4">
         <v>2</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="4">
         <v>20040215</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="4">
         <v>3</v>
       </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
+      <c r="S2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4">
         <v>-88.85</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>41.85</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>19.248999999999999</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="4">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4">
         <v>2005</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="4">
         <v>2002</v>
       </c>
-      <c r="J3" s="1">
-        <v>4</v>
-      </c>
-      <c r="K3">
+      <c r="J3" s="4">
+        <v>4</v>
+      </c>
+      <c r="K3" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N3">
-        <v>4</v>
-      </c>
-      <c r="O3">
+      <c r="N3" s="4">
+        <v>4</v>
+      </c>
+      <c r="O3" s="4">
         <v>15</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="4">
         <v>2</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="4">
         <v>20050215</v>
       </c>
-      <c r="R3">
-        <v>4</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
+      <c r="R3" s="4">
+        <v>4</v>
+      </c>
+      <c r="S3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4">
         <v>-88.85</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>41.85</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>29.286000000000001</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F4">
-        <v>12</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="4">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4">
         <v>2006</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="4">
         <v>2002</v>
       </c>
-      <c r="J4" s="1">
-        <v>4</v>
-      </c>
-      <c r="K4">
+      <c r="J4" s="4">
+        <v>4</v>
+      </c>
+      <c r="K4" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N4">
-        <v>4</v>
-      </c>
-      <c r="O4">
+      <c r="N4" s="4">
+        <v>4</v>
+      </c>
+      <c r="O4" s="4">
         <v>15</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="4">
         <v>2</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="4">
         <v>20060215</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="4">
         <v>5</v>
       </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
+      <c r="S4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4">
         <v>-88.85</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>41.85</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>20.033999999999999</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="4">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4">
         <v>2007</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="4">
         <v>2002</v>
       </c>
-      <c r="J5" s="1">
-        <v>4</v>
-      </c>
-      <c r="K5">
+      <c r="J5" s="4">
+        <v>4</v>
+      </c>
+      <c r="K5" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N5">
-        <v>4</v>
-      </c>
-      <c r="O5">
+      <c r="N5" s="4">
+        <v>4</v>
+      </c>
+      <c r="O5" s="4">
         <v>15</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="4">
         <v>2</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="4">
         <v>20070215</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="4">
         <v>6</v>
       </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
+      <c r="S5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4">
         <v>-88.85</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>41.85</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>5.6429999999999998</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="4">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4">
         <v>2008</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="4">
         <v>2002</v>
       </c>
-      <c r="J6" s="1">
-        <v>4</v>
-      </c>
-      <c r="K6">
+      <c r="J6" s="4">
+        <v>4</v>
+      </c>
+      <c r="K6" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N6">
-        <v>4</v>
-      </c>
-      <c r="O6">
+      <c r="N6" s="4">
+        <v>4</v>
+      </c>
+      <c r="O6" s="4">
         <v>15</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="4">
         <v>2</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="4">
         <v>20080215</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="4">
         <v>7</v>
       </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
+      <c r="S6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4">
         <v>-88.85</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>41.85</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>8.8209999999999997</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F7">
-        <v>12</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="4">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4">
         <v>2009</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="4">
         <v>2002</v>
       </c>
-      <c r="J7" s="1">
-        <v>4</v>
-      </c>
-      <c r="K7">
+      <c r="J7" s="4">
+        <v>4</v>
+      </c>
+      <c r="K7" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
-      <c r="O7">
+      <c r="N7" s="4">
+        <v>4</v>
+      </c>
+      <c r="O7" s="4">
         <v>15</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="4">
         <v>2</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="4">
         <v>20090215</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="4">
         <v>8</v>
       </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
+      <c r="S7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4">
         <v>-88.85</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>41.85</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>14.571</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="4">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4">
         <v>2010</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="4">
         <v>2002</v>
       </c>
-      <c r="J8" s="1">
-        <v>4</v>
-      </c>
-      <c r="K8">
+      <c r="J8" s="4">
+        <v>4</v>
+      </c>
+      <c r="K8" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N8">
-        <v>4</v>
-      </c>
-      <c r="O8">
+      <c r="N8" s="4">
+        <v>4</v>
+      </c>
+      <c r="O8" s="4">
         <v>15</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="4">
         <v>2</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="4">
         <v>20100215</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="4">
         <v>9</v>
       </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
+      <c r="S8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4">
         <v>-88.85</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="4">
         <v>41.85</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>13.677</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F9">
-        <v>12</v>
-      </c>
-      <c r="G9">
+      <c r="F9" s="4">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4">
         <v>2011</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="4">
         <v>2002</v>
       </c>
-      <c r="J9" s="1">
-        <v>4</v>
-      </c>
-      <c r="K9">
+      <c r="J9" s="4">
+        <v>4</v>
+      </c>
+      <c r="K9" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N9">
-        <v>4</v>
-      </c>
-      <c r="O9">
+      <c r="N9" s="4">
+        <v>4</v>
+      </c>
+      <c r="O9" s="4">
         <v>15</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="4">
         <v>2</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="4">
         <v>20110215</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="4">
         <v>10</v>
       </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="S9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
         <v>2</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="4">
         <v>-88.23</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <v>40.08</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>25.126000000000001</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F10">
-        <v>12</v>
-      </c>
-      <c r="G10">
+      <c r="F10" s="4">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4">
         <v>2004</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="4">
         <v>2002</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="1">
-        <v>4</v>
-      </c>
-      <c r="K10">
+      <c r="J10" s="4">
+        <v>4</v>
+      </c>
+      <c r="K10" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N10">
-        <v>4</v>
-      </c>
-      <c r="O10">
+      <c r="N10" s="4">
+        <v>4</v>
+      </c>
+      <c r="O10" s="4">
         <v>15</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="4">
         <v>2</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="4">
         <v>20040215</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="4">
         <v>3</v>
       </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="S10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
         <v>2</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>-88.23</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="4">
         <v>40.08</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="4">
         <v>30.975000000000001</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F11">
-        <v>12</v>
-      </c>
-      <c r="G11">
+      <c r="F11" s="4">
+        <v>12</v>
+      </c>
+      <c r="G11" s="4">
         <v>2005</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="4">
         <v>2002</v>
       </c>
-      <c r="J11" s="1">
-        <v>4</v>
-      </c>
-      <c r="K11">
+      <c r="J11" s="4">
+        <v>4</v>
+      </c>
+      <c r="K11" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N11">
-        <v>4</v>
-      </c>
-      <c r="O11">
+      <c r="N11" s="4">
+        <v>4</v>
+      </c>
+      <c r="O11" s="4">
         <v>15</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="4">
         <v>2</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="4">
         <v>20050215</v>
       </c>
-      <c r="R11">
-        <v>4</v>
-      </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="R11" s="4">
+        <v>4</v>
+      </c>
+      <c r="S11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
         <v>2</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="4">
         <v>-88.23</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>40.08</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="4">
         <v>44.404000000000003</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F12">
-        <v>12</v>
-      </c>
-      <c r="G12">
+      <c r="F12" s="4">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4">
         <v>2006</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="4">
         <v>2002</v>
       </c>
-      <c r="J12" s="1">
-        <v>4</v>
-      </c>
-      <c r="K12">
+      <c r="J12" s="4">
+        <v>4</v>
+      </c>
+      <c r="K12" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N12">
-        <v>4</v>
-      </c>
-      <c r="O12">
+      <c r="N12" s="4">
+        <v>4</v>
+      </c>
+      <c r="O12" s="4">
         <v>15</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="4">
         <v>2</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="4">
         <v>20060215</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="4">
         <v>5</v>
       </c>
-      <c r="S12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="S12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
         <v>2</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="4">
         <v>-88.23</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="4">
         <v>40.08</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="4">
         <v>38.338999999999999</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F13">
-        <v>12</v>
-      </c>
-      <c r="G13">
+      <c r="F13" s="4">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4">
         <v>2007</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="4">
         <v>2002</v>
       </c>
-      <c r="J13" s="1">
-        <v>4</v>
-      </c>
-      <c r="K13">
+      <c r="J13" s="4">
+        <v>4</v>
+      </c>
+      <c r="K13" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N13">
-        <v>4</v>
-      </c>
-      <c r="O13">
+      <c r="N13" s="4">
+        <v>4</v>
+      </c>
+      <c r="O13" s="4">
         <v>15</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="4">
         <v>2</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="4">
         <v>20070215</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="4">
         <v>6</v>
       </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="S13" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
         <v>2</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="4">
         <v>-88.23</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="4">
         <v>40.08</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="4">
         <v>36.173000000000002</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F14">
-        <v>12</v>
-      </c>
-      <c r="G14">
+      <c r="F14" s="4">
+        <v>12</v>
+      </c>
+      <c r="G14" s="4">
         <v>2008</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="4">
         <v>2002</v>
       </c>
-      <c r="J14" s="1">
-        <v>4</v>
-      </c>
-      <c r="K14">
+      <c r="J14" s="4">
+        <v>4</v>
+      </c>
+      <c r="K14" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N14">
-        <v>4</v>
-      </c>
-      <c r="O14">
+      <c r="N14" s="4">
+        <v>4</v>
+      </c>
+      <c r="O14" s="4">
         <v>15</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="4">
         <v>2</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="4">
         <v>20080215</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="4">
         <v>7</v>
       </c>
-      <c r="S14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="S14" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
         <v>2</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="4">
         <v>-88.23</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>40.08</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="4">
         <v>23.177</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F15">
-        <v>12</v>
-      </c>
-      <c r="G15">
+      <c r="F15" s="4">
+        <v>12</v>
+      </c>
+      <c r="G15" s="4">
         <v>2009</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="4">
         <v>2002</v>
       </c>
-      <c r="J15" s="1">
-        <v>4</v>
-      </c>
-      <c r="K15">
+      <c r="J15" s="4">
+        <v>4</v>
+      </c>
+      <c r="K15" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N15">
-        <v>4</v>
-      </c>
-      <c r="O15">
+      <c r="N15" s="4">
+        <v>4</v>
+      </c>
+      <c r="O15" s="4">
         <v>15</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="4">
         <v>2</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="4">
         <v>20090215</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="4">
         <v>8</v>
       </c>
-      <c r="S15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="S15" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
         <v>2</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="4">
         <v>-88.23</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="4">
         <v>40.08</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="4">
         <v>25.343</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F16">
-        <v>12</v>
-      </c>
-      <c r="G16">
+      <c r="F16" s="4">
+        <v>12</v>
+      </c>
+      <c r="G16" s="4">
         <v>2010</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="4">
         <v>2002</v>
       </c>
-      <c r="J16" s="1">
-        <v>4</v>
-      </c>
-      <c r="K16">
+      <c r="J16" s="4">
+        <v>4</v>
+      </c>
+      <c r="K16" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N16">
-        <v>4</v>
-      </c>
-      <c r="O16">
+      <c r="N16" s="4">
+        <v>4</v>
+      </c>
+      <c r="O16" s="4">
         <v>15</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="4">
         <v>2</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="4">
         <v>20100215</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="4">
         <v>9</v>
       </c>
-      <c r="S16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="S16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
         <v>2</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="4">
         <v>-88.23</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="4">
         <v>40.08</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="4">
         <v>27.076000000000001</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F17">
-        <v>12</v>
-      </c>
-      <c r="G17">
+      <c r="F17" s="4">
+        <v>12</v>
+      </c>
+      <c r="G17" s="4">
         <v>2011</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="4">
         <v>2002</v>
       </c>
-      <c r="J17" s="1">
-        <v>4</v>
-      </c>
-      <c r="K17">
+      <c r="J17" s="4">
+        <v>4</v>
+      </c>
+      <c r="K17" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N17">
-        <v>4</v>
-      </c>
-      <c r="O17">
+      <c r="N17" s="4">
+        <v>4</v>
+      </c>
+      <c r="O17" s="4">
         <v>15</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="4">
         <v>2</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="4">
         <v>20110215</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="4">
         <v>10</v>
       </c>
-      <c r="S17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A18">
+      <c r="S17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
         <v>3</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="4">
         <v>-88.67</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="4">
         <v>37.450000000000003</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="4">
         <v>37.256</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F18">
-        <v>12</v>
-      </c>
-      <c r="G18">
+      <c r="F18" s="4">
+        <v>12</v>
+      </c>
+      <c r="G18" s="4">
         <v>2004</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="4">
         <v>2002</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="1">
-        <v>4</v>
-      </c>
-      <c r="K18">
+      <c r="J18" s="4">
+        <v>4</v>
+      </c>
+      <c r="K18" s="4">
         <v>1.32764411</v>
       </c>
-      <c r="N18">
-        <v>4</v>
-      </c>
-      <c r="O18">
+      <c r="N18" s="4">
+        <v>4</v>
+      </c>
+      <c r="O18" s="4">
         <v>15</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="4">
         <v>2</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="4">
         <v>20040215</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="4">
         <v>3</v>
       </c>
-      <c r="S18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="S18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
         <v>3</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="4">
         <v>-88.67</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="4">
         <v>37.450000000000003</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="4">
         <v>27.509</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F19">
-        <v>12</v>
-      </c>
-      <c r="G19">
+      <c r="F19" s="4">
+        <v>12</v>
+      </c>
+      <c r="G19" s="4">
         <v>2005</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="4">
         <v>2002</v>
       </c>
-      <c r="J19" s="1">
-        <v>4</v>
-      </c>
-      <c r="K19">
+      <c r="J19" s="4">
+        <v>4</v>
+      </c>
+      <c r="K19" s="4">
         <v>1.32764411</v>
       </c>
-      <c r="N19">
-        <v>4</v>
-      </c>
-      <c r="O19">
+      <c r="N19" s="4">
+        <v>4</v>
+      </c>
+      <c r="O19" s="4">
         <v>15</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="4">
         <v>2</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="4">
         <v>20050215</v>
       </c>
-      <c r="R19">
-        <v>4</v>
-      </c>
-      <c r="S19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="R19" s="4">
+        <v>4</v>
+      </c>
+      <c r="S19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
         <v>3</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="4">
         <v>-88.67</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="4">
         <v>37.450000000000003</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="4">
         <v>39.421999999999997</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F20">
-        <v>12</v>
-      </c>
-      <c r="G20">
+      <c r="F20" s="4">
+        <v>12</v>
+      </c>
+      <c r="G20" s="4">
         <v>2006</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="4">
         <v>2002</v>
       </c>
-      <c r="J20" s="1">
-        <v>4</v>
-      </c>
-      <c r="K20">
+      <c r="J20" s="4">
+        <v>4</v>
+      </c>
+      <c r="K20" s="4">
         <v>1.32764411</v>
       </c>
-      <c r="N20">
-        <v>4</v>
-      </c>
-      <c r="O20">
+      <c r="N20" s="4">
+        <v>4</v>
+      </c>
+      <c r="O20" s="4">
         <v>15</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="4">
         <v>2</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="4">
         <v>20060215</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="4">
         <v>5</v>
       </c>
-      <c r="S20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="S20" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
         <v>3</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="4">
         <v>-88.67</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="4">
         <v>37.450000000000003</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="4">
         <v>39.639000000000003</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F21">
-        <v>12</v>
-      </c>
-      <c r="G21">
+      <c r="F21" s="4">
+        <v>12</v>
+      </c>
+      <c r="G21" s="4">
         <v>2007</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="4">
         <v>2002</v>
       </c>
-      <c r="J21" s="1">
-        <v>4</v>
-      </c>
-      <c r="K21">
+      <c r="J21" s="4">
+        <v>4</v>
+      </c>
+      <c r="K21" s="4">
         <v>1.32764411</v>
       </c>
-      <c r="N21">
-        <v>4</v>
-      </c>
-      <c r="O21">
+      <c r="N21" s="4">
+        <v>4</v>
+      </c>
+      <c r="O21" s="4">
         <v>15</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="4">
         <v>2</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="4">
         <v>20070215</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="4">
         <v>6</v>
       </c>
-      <c r="S21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="S21" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
         <v>3</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="4">
         <v>-88.67</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="4">
         <v>37.450000000000003</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="4">
         <v>32.274000000000001</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F22">
-        <v>12</v>
-      </c>
-      <c r="G22">
+      <c r="F22" s="4">
+        <v>12</v>
+      </c>
+      <c r="G22" s="4">
         <v>2008</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="4">
         <v>2002</v>
       </c>
-      <c r="J22" s="1">
-        <v>4</v>
-      </c>
-      <c r="K22">
+      <c r="J22" s="4">
+        <v>4</v>
+      </c>
+      <c r="K22" s="4">
         <v>1.32764411</v>
       </c>
-      <c r="N22">
-        <v>4</v>
-      </c>
-      <c r="O22">
+      <c r="N22" s="4">
+        <v>4</v>
+      </c>
+      <c r="O22" s="4">
         <v>15</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="4">
         <v>2</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="4">
         <v>20080215</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="4">
         <v>7</v>
       </c>
-      <c r="S22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="S22" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
         <v>3</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="4">
         <v>-88.67</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="4">
         <v>37.450000000000003</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="4">
         <v>17.111999999999998</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F23">
-        <v>12</v>
-      </c>
-      <c r="G23">
+      <c r="F23" s="4">
+        <v>12</v>
+      </c>
+      <c r="G23" s="4">
         <v>2009</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="4">
         <v>2002</v>
       </c>
-      <c r="J23" s="1">
-        <v>4</v>
-      </c>
-      <c r="K23">
+      <c r="J23" s="4">
+        <v>4</v>
+      </c>
+      <c r="K23" s="4">
         <v>1.32764411</v>
       </c>
-      <c r="N23">
-        <v>4</v>
-      </c>
-      <c r="O23">
+      <c r="N23" s="4">
+        <v>4</v>
+      </c>
+      <c r="O23" s="4">
         <v>15</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="4">
         <v>2</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="4">
         <v>20090215</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="4">
         <v>8</v>
       </c>
-      <c r="S23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="S23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
         <v>3</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="4">
         <v>-88.67</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="4">
         <v>37.450000000000003</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="4">
         <v>21.876999999999999</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F24">
-        <v>12</v>
-      </c>
-      <c r="G24">
+      <c r="F24" s="4">
+        <v>12</v>
+      </c>
+      <c r="G24" s="4">
         <v>2010</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="4">
         <v>2002</v>
       </c>
-      <c r="J24" s="1">
-        <v>4</v>
-      </c>
-      <c r="K24">
+      <c r="J24" s="4">
+        <v>4</v>
+      </c>
+      <c r="K24" s="4">
         <v>1.32764411</v>
       </c>
-      <c r="N24">
-        <v>4</v>
-      </c>
-      <c r="O24">
+      <c r="N24" s="4">
+        <v>4</v>
+      </c>
+      <c r="O24" s="4">
         <v>15</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="4">
         <v>2</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="4">
         <v>20100215</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="4">
         <v>9</v>
       </c>
-      <c r="S24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="S24" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
         <v>3</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="4">
         <v>-88.67</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="4">
         <v>37.450000000000003</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="4">
         <v>23.177</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F25">
-        <v>12</v>
-      </c>
-      <c r="G25">
+      <c r="F25" s="4">
+        <v>12</v>
+      </c>
+      <c r="G25" s="4">
         <v>2011</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="4">
         <v>2002</v>
       </c>
-      <c r="J25" s="1">
-        <v>4</v>
-      </c>
-      <c r="K25">
+      <c r="J25" s="4">
+        <v>4</v>
+      </c>
+      <c r="K25" s="4">
         <v>1.32764411</v>
       </c>
-      <c r="N25">
-        <v>4</v>
-      </c>
-      <c r="O25">
+      <c r="N25" s="4">
+        <v>4</v>
+      </c>
+      <c r="O25" s="4">
         <v>15</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="4">
         <v>2</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="4">
         <v>20110215</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="4">
         <v>10</v>
       </c>
-      <c r="S25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>4</v>
-      </c>
-      <c r="B26">
+      <c r="S25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
+        <v>4</v>
+      </c>
+      <c r="B26" s="4">
         <v>-89.94</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="4">
         <v>40.299999999999997</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="4">
         <v>3.6819999999999999</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F26">
-        <v>12</v>
-      </c>
-      <c r="G26">
+      <c r="F26" s="4">
+        <v>12</v>
+      </c>
+      <c r="G26" s="4">
         <v>2006</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="4">
         <v>2004</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
+      <c r="J26" s="4">
+        <v>1</v>
+      </c>
+      <c r="K26" s="4">
         <v>1.4648147819999999</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="4">
         <v>0</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="4">
         <v>15</v>
       </c>
-      <c r="P26">
-        <v>12</v>
-      </c>
-      <c r="Q26">
+      <c r="P26" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q26" s="4">
         <v>20061215</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="4">
         <v>3</v>
       </c>
-      <c r="S26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>4</v>
-      </c>
-      <c r="B27">
+      <c r="S26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
+        <v>4</v>
+      </c>
+      <c r="B27" s="4">
         <v>-89.94</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="4">
         <v>40.299999999999997</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="4">
         <v>14.891</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F27">
-        <v>12</v>
-      </c>
-      <c r="G27">
+      <c r="F27" s="4">
+        <v>12</v>
+      </c>
+      <c r="G27" s="4">
         <v>2007</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="4">
         <v>2004</v>
       </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
+      <c r="J27" s="4">
+        <v>1</v>
+      </c>
+      <c r="K27" s="4">
         <v>1.4648147819999999</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="4">
         <v>0</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="4">
         <v>15</v>
       </c>
-      <c r="P27">
-        <v>12</v>
-      </c>
-      <c r="Q27">
+      <c r="P27" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q27" s="4">
         <v>20071215</v>
       </c>
-      <c r="R27">
-        <v>4</v>
-      </c>
-      <c r="S27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>4</v>
-      </c>
-      <c r="B28">
+      <c r="R27" s="4">
+        <v>4</v>
+      </c>
+      <c r="S27" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
+        <v>4</v>
+      </c>
+      <c r="B28" s="4">
         <v>-89.94</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="4">
         <v>40.299999999999997</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="4">
         <v>34.332000000000001</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F28">
-        <v>12</v>
-      </c>
-      <c r="G28">
+      <c r="F28" s="4">
+        <v>12</v>
+      </c>
+      <c r="G28" s="4">
         <v>2008</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="4">
         <v>2004</v>
       </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
+      <c r="J28" s="4">
+        <v>1</v>
+      </c>
+      <c r="K28" s="4">
         <v>1.4648147819999999</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="4">
         <v>0</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="4">
         <v>15</v>
       </c>
-      <c r="P28">
-        <v>12</v>
-      </c>
-      <c r="Q28">
+      <c r="P28" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q28" s="4">
         <v>20081215</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="4">
         <v>5</v>
       </c>
-      <c r="S28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>4</v>
-      </c>
-      <c r="B29">
+      <c r="S28" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
+        <v>4</v>
+      </c>
+      <c r="B29" s="4">
         <v>-89.94</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="4">
         <v>40.299999999999997</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="4">
         <v>13.917</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F29">
-        <v>12</v>
-      </c>
-      <c r="G29">
+      <c r="F29" s="4">
+        <v>12</v>
+      </c>
+      <c r="G29" s="4">
         <v>2009</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="4">
         <v>2004</v>
       </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
+      <c r="J29" s="4">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4">
         <v>1.4648147819999999</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="4">
         <v>0</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="4">
         <v>15</v>
       </c>
-      <c r="P29">
-        <v>12</v>
-      </c>
-      <c r="Q29">
+      <c r="P29" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q29" s="4">
         <v>20091215</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="4">
         <v>6</v>
       </c>
-      <c r="S29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30">
+      <c r="S29" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
+        <v>4</v>
+      </c>
+      <c r="B30" s="4">
         <v>-89.94</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="4">
         <v>40.299999999999997</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="4">
         <v>17.327999999999999</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F30">
-        <v>12</v>
-      </c>
-      <c r="G30">
+      <c r="F30" s="4">
+        <v>12</v>
+      </c>
+      <c r="G30" s="4">
         <v>2010</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="4">
         <v>2004</v>
       </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
+      <c r="J30" s="4">
+        <v>1</v>
+      </c>
+      <c r="K30" s="4">
         <v>1.4648147819999999</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="4">
         <v>0</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="4">
         <v>15</v>
       </c>
-      <c r="P30">
-        <v>12</v>
-      </c>
-      <c r="Q30">
+      <c r="P30" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q30" s="4">
         <v>20101215</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="4">
         <v>7</v>
       </c>
-      <c r="S30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>4</v>
-      </c>
-      <c r="B31">
+      <c r="S30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
+        <v>4</v>
+      </c>
+      <c r="B31" s="4">
         <v>-89.94</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="4">
         <v>40.299999999999997</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="4">
         <v>19.224</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F31">
-        <v>12</v>
-      </c>
-      <c r="G31">
+      <c r="F31" s="4">
+        <v>12</v>
+      </c>
+      <c r="G31" s="4">
         <v>2011</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="4">
         <v>2004</v>
       </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
+      <c r="J31" s="4">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4">
         <v>1.4648147819999999</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="4">
         <v>0</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="4">
         <v>15</v>
       </c>
-      <c r="P31">
-        <v>12</v>
-      </c>
-      <c r="Q31">
+      <c r="P31" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q31" s="4">
         <v>20111215</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="4">
         <v>8</v>
       </c>
-      <c r="S31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A32">
+      <c r="S31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
         <v>5</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="4">
         <v>-90.82</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="4">
         <v>39.81</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="4">
         <v>36.131999999999998</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F32">
-        <v>12</v>
-      </c>
-      <c r="G32">
+      <c r="F32" s="4">
+        <v>12</v>
+      </c>
+      <c r="G32" s="4">
         <v>2006</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="4">
         <v>2004</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J32">
-        <v>4</v>
-      </c>
-      <c r="K32">
+      <c r="J32" s="4">
+        <v>4</v>
+      </c>
+      <c r="K32" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N32">
-        <v>4</v>
-      </c>
-      <c r="O32">
+      <c r="N32" s="4">
+        <v>4</v>
+      </c>
+      <c r="O32" s="4">
         <v>15</v>
       </c>
-      <c r="P32">
-        <v>12</v>
-      </c>
-      <c r="Q32">
+      <c r="P32" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q32" s="4">
         <v>20061215</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="4">
         <v>3</v>
       </c>
-      <c r="S32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A33">
+      <c r="S32" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
         <v>5</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="4">
         <v>-90.82</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="4">
         <v>39.81</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="4">
         <v>36.241999999999997</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F33">
-        <v>12</v>
-      </c>
-      <c r="G33">
+      <c r="F33" s="4">
+        <v>12</v>
+      </c>
+      <c r="G33" s="4">
         <v>2007</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="4">
         <v>2004</v>
       </c>
-      <c r="J33">
-        <v>4</v>
-      </c>
-      <c r="K33">
+      <c r="J33" s="4">
+        <v>4</v>
+      </c>
+      <c r="K33" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N33">
-        <v>4</v>
-      </c>
-      <c r="O33">
+      <c r="N33" s="4">
+        <v>4</v>
+      </c>
+      <c r="O33" s="4">
         <v>15</v>
       </c>
-      <c r="P33">
-        <v>12</v>
-      </c>
-      <c r="Q33">
+      <c r="P33" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q33" s="4">
         <v>20071215</v>
       </c>
-      <c r="R33">
-        <v>4</v>
-      </c>
-      <c r="S33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A34">
+      <c r="R33" s="4">
+        <v>4</v>
+      </c>
+      <c r="S33" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
         <v>5</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="4">
         <v>-90.82</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="4">
         <v>39.81</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="4">
         <v>32.411999999999999</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F34">
-        <v>12</v>
-      </c>
-      <c r="G34">
+      <c r="F34" s="4">
+        <v>12</v>
+      </c>
+      <c r="G34" s="4">
         <v>2008</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="4">
         <v>2004</v>
       </c>
-      <c r="J34">
-        <v>4</v>
-      </c>
-      <c r="K34">
+      <c r="J34" s="4">
+        <v>4</v>
+      </c>
+      <c r="K34" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N34">
-        <v>4</v>
-      </c>
-      <c r="O34">
+      <c r="N34" s="4">
+        <v>4</v>
+      </c>
+      <c r="O34" s="4">
         <v>15</v>
       </c>
-      <c r="P34">
-        <v>12</v>
-      </c>
-      <c r="Q34">
+      <c r="P34" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="4">
         <v>20081215</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="4">
         <v>5</v>
       </c>
-      <c r="S34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A35">
+      <c r="S34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
         <v>5</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="4">
         <v>-90.82</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="4">
         <v>39.81</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="4">
         <v>20.474</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F35">
-        <v>12</v>
-      </c>
-      <c r="G35">
+      <c r="F35" s="4">
+        <v>12</v>
+      </c>
+      <c r="G35" s="4">
         <v>2009</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="4">
         <v>2004</v>
       </c>
-      <c r="J35">
-        <v>4</v>
-      </c>
-      <c r="K35">
+      <c r="J35" s="4">
+        <v>4</v>
+      </c>
+      <c r="K35" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N35">
-        <v>4</v>
-      </c>
-      <c r="O35">
+      <c r="N35" s="4">
+        <v>4</v>
+      </c>
+      <c r="O35" s="4">
         <v>15</v>
       </c>
-      <c r="P35">
-        <v>12</v>
-      </c>
-      <c r="Q35">
+      <c r="P35" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q35" s="4">
         <v>20091215</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="4">
         <v>6</v>
       </c>
-      <c r="S35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A36">
+      <c r="S35" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
         <v>5</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="4">
         <v>-90.82</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="4">
         <v>39.81</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="4">
         <v>17.518999999999998</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F36">
-        <v>12</v>
-      </c>
-      <c r="G36">
+      <c r="F36" s="4">
+        <v>12</v>
+      </c>
+      <c r="G36" s="4">
         <v>2010</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="4">
         <v>2004</v>
       </c>
-      <c r="J36">
-        <v>4</v>
-      </c>
-      <c r="K36">
+      <c r="J36" s="4">
+        <v>4</v>
+      </c>
+      <c r="K36" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N36">
-        <v>4</v>
-      </c>
-      <c r="O36">
+      <c r="N36" s="4">
+        <v>4</v>
+      </c>
+      <c r="O36" s="4">
         <v>15</v>
       </c>
-      <c r="P36">
-        <v>12</v>
-      </c>
-      <c r="Q36">
+      <c r="P36" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q36" s="4">
         <v>20101215</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="4">
         <v>7</v>
       </c>
-      <c r="S36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A37">
+      <c r="S36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
         <v>5</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="4">
         <v>-90.82</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="4">
         <v>39.81</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="4">
         <v>14.125</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F37">
-        <v>12</v>
-      </c>
-      <c r="G37">
+      <c r="F37" s="4">
+        <v>12</v>
+      </c>
+      <c r="G37" s="4">
         <v>2011</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="4">
         <v>2004</v>
       </c>
-      <c r="J37">
-        <v>4</v>
-      </c>
-      <c r="K37">
+      <c r="J37" s="4">
+        <v>4</v>
+      </c>
+      <c r="K37" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N37">
-        <v>4</v>
-      </c>
-      <c r="O37">
+      <c r="N37" s="4">
+        <v>4</v>
+      </c>
+      <c r="O37" s="4">
         <v>15</v>
       </c>
-      <c r="P37">
-        <v>12</v>
-      </c>
-      <c r="Q37">
+      <c r="P37" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q37" s="4">
         <v>20111215</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="4">
         <v>8</v>
       </c>
-      <c r="S37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A38">
+      <c r="S37" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
         <v>6</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="4">
         <v>-88.96</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="4">
         <v>38.950000000000003</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="4">
         <v>9.9649999999999999</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F38">
-        <v>12</v>
-      </c>
-      <c r="G38">
+      <c r="F38" s="4">
+        <v>12</v>
+      </c>
+      <c r="G38" s="4">
         <v>2006</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="4">
         <v>2004</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J38">
-        <v>4</v>
-      </c>
-      <c r="K38">
+      <c r="J38" s="4">
+        <v>4</v>
+      </c>
+      <c r="K38" s="4">
         <v>1.455909967</v>
       </c>
-      <c r="N38">
-        <v>4</v>
-      </c>
-      <c r="O38">
+      <c r="N38" s="4">
+        <v>4</v>
+      </c>
+      <c r="O38" s="4">
         <v>15</v>
       </c>
-      <c r="P38">
-        <v>12</v>
-      </c>
-      <c r="Q38">
+      <c r="P38" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q38" s="4">
         <v>20061215</v>
       </c>
-      <c r="R38">
+      <c r="R38" s="4">
         <v>3</v>
       </c>
-      <c r="S38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A39">
+      <c r="S38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
         <v>6</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="4">
         <v>-88.96</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="4">
         <v>38.950000000000003</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="4">
         <v>8.5540000000000003</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F39">
-        <v>12</v>
-      </c>
-      <c r="G39">
+      <c r="F39" s="4">
+        <v>12</v>
+      </c>
+      <c r="G39" s="4">
         <v>2007</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="4">
         <v>2004</v>
       </c>
-      <c r="J39">
-        <v>4</v>
-      </c>
-      <c r="K39">
+      <c r="J39" s="4">
+        <v>4</v>
+      </c>
+      <c r="K39" s="4">
         <v>1.455909967</v>
       </c>
-      <c r="N39">
-        <v>4</v>
-      </c>
-      <c r="O39">
+      <c r="N39" s="4">
+        <v>4</v>
+      </c>
+      <c r="O39" s="4">
         <v>15</v>
       </c>
-      <c r="P39">
-        <v>12</v>
-      </c>
-      <c r="Q39">
+      <c r="P39" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q39" s="4">
         <v>20071215</v>
       </c>
-      <c r="R39">
-        <v>4</v>
-      </c>
-      <c r="S39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A40">
+      <c r="R39" s="4">
+        <v>4</v>
+      </c>
+      <c r="S39" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
         <v>6</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="4">
         <v>-88.96</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="4">
         <v>38.950000000000003</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="4">
         <v>17.113</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F40">
-        <v>12</v>
-      </c>
-      <c r="G40">
+      <c r="F40" s="4">
+        <v>12</v>
+      </c>
+      <c r="G40" s="4">
         <v>2008</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="4">
         <v>2004</v>
       </c>
-      <c r="J40">
-        <v>4</v>
-      </c>
-      <c r="K40">
+      <c r="J40" s="4">
+        <v>4</v>
+      </c>
+      <c r="K40" s="4">
         <v>1.455909967</v>
       </c>
-      <c r="N40">
-        <v>4</v>
-      </c>
-      <c r="O40">
+      <c r="N40" s="4">
+        <v>4</v>
+      </c>
+      <c r="O40" s="4">
         <v>15</v>
       </c>
-      <c r="P40">
-        <v>12</v>
-      </c>
-      <c r="Q40">
+      <c r="P40" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="4">
         <v>20081215</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="4">
         <v>5</v>
       </c>
-      <c r="S40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A41">
+      <c r="S40" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
         <v>6</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="4">
         <v>-88.96</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="4">
         <v>38.950000000000003</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="4">
         <v>10.505000000000001</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F41">
-        <v>12</v>
-      </c>
-      <c r="G41">
+      <c r="F41" s="4">
+        <v>12</v>
+      </c>
+      <c r="G41" s="4">
         <v>2009</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="4">
         <v>2004</v>
       </c>
-      <c r="J41">
-        <v>4</v>
-      </c>
-      <c r="K41">
+      <c r="J41" s="4">
+        <v>4</v>
+      </c>
+      <c r="K41" s="4">
         <v>1.455909967</v>
       </c>
-      <c r="N41">
-        <v>4</v>
-      </c>
-      <c r="O41">
+      <c r="N41" s="4">
+        <v>4</v>
+      </c>
+      <c r="O41" s="4">
         <v>15</v>
       </c>
-      <c r="P41">
-        <v>12</v>
-      </c>
-      <c r="Q41">
+      <c r="P41" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q41" s="4">
         <v>20091215</v>
       </c>
-      <c r="R41">
+      <c r="R41" s="4">
         <v>6</v>
       </c>
-      <c r="S41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A42">
+      <c r="S41" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="4">
         <v>6</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="4">
         <v>-88.96</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="4">
         <v>38.950000000000003</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="4">
         <v>21.876000000000001</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F42">
-        <v>12</v>
-      </c>
-      <c r="G42">
+      <c r="F42" s="4">
+        <v>12</v>
+      </c>
+      <c r="G42" s="4">
         <v>2010</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="4">
         <v>2004</v>
       </c>
-      <c r="J42">
-        <v>4</v>
-      </c>
-      <c r="K42">
+      <c r="J42" s="4">
+        <v>4</v>
+      </c>
+      <c r="K42" s="4">
         <v>1.455909967</v>
       </c>
-      <c r="N42">
-        <v>4</v>
-      </c>
-      <c r="O42">
+      <c r="N42" s="4">
+        <v>4</v>
+      </c>
+      <c r="O42" s="4">
         <v>15</v>
       </c>
-      <c r="P42">
-        <v>12</v>
-      </c>
-      <c r="Q42">
+      <c r="P42" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q42" s="4">
         <v>20101215</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="4">
         <v>7</v>
       </c>
-      <c r="S42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A43">
+      <c r="S42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="4">
         <v>6</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="4">
         <v>-88.96</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="4">
         <v>38.950000000000003</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="4">
         <v>21.117999999999999</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F43">
-        <v>12</v>
-      </c>
-      <c r="G43">
+      <c r="F43" s="4">
+        <v>12</v>
+      </c>
+      <c r="G43" s="4">
         <v>2011</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="4">
         <v>2004</v>
       </c>
-      <c r="J43">
-        <v>4</v>
-      </c>
-      <c r="K43">
+      <c r="J43" s="4">
+        <v>4</v>
+      </c>
+      <c r="K43" s="4">
         <v>1.455909967</v>
       </c>
-      <c r="N43">
-        <v>4</v>
-      </c>
-      <c r="O43">
+      <c r="N43" s="4">
+        <v>4</v>
+      </c>
+      <c r="O43" s="4">
         <v>15</v>
       </c>
-      <c r="P43">
-        <v>12</v>
-      </c>
-      <c r="Q43">
+      <c r="P43" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q43" s="4">
         <v>20111215</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="4">
         <v>8</v>
       </c>
-      <c r="S43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A44">
+      <c r="S43" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="4">
         <v>7</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="4">
         <v>-88.39</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="4">
         <v>38.380000000000003</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="4">
         <v>39.055</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F44">
-        <v>12</v>
-      </c>
-      <c r="G44">
+      <c r="F44" s="4">
+        <v>12</v>
+      </c>
+      <c r="G44" s="4">
         <v>2006</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="4">
         <v>2004</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J44">
-        <v>4</v>
-      </c>
-      <c r="K44">
+      <c r="J44" s="4">
+        <v>4</v>
+      </c>
+      <c r="K44" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N44">
-        <v>4</v>
-      </c>
-      <c r="O44">
+      <c r="N44" s="4">
+        <v>4</v>
+      </c>
+      <c r="O44" s="4">
         <v>15</v>
       </c>
-      <c r="P44">
-        <v>12</v>
-      </c>
-      <c r="Q44">
+      <c r="P44" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q44" s="4">
         <v>20061215</v>
       </c>
-      <c r="R44">
+      <c r="R44" s="4">
         <v>3</v>
       </c>
-      <c r="S44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A45">
+      <c r="S44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="4">
         <v>7</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="4">
         <v>-88.39</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="4">
         <v>38.380000000000003</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="4">
         <v>33.381999999999998</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F45">
-        <v>12</v>
-      </c>
-      <c r="G45">
+      <c r="F45" s="4">
+        <v>12</v>
+      </c>
+      <c r="G45" s="4">
         <v>2007</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="4">
         <v>2004</v>
       </c>
-      <c r="J45">
-        <v>4</v>
-      </c>
-      <c r="K45">
+      <c r="J45" s="4">
+        <v>4</v>
+      </c>
+      <c r="K45" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N45">
-        <v>4</v>
-      </c>
-      <c r="O45">
+      <c r="N45" s="4">
+        <v>4</v>
+      </c>
+      <c r="O45" s="4">
         <v>15</v>
       </c>
-      <c r="P45">
-        <v>12</v>
-      </c>
-      <c r="Q45">
+      <c r="P45" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q45" s="4">
         <v>20071215</v>
       </c>
-      <c r="R45">
-        <v>4</v>
-      </c>
-      <c r="S45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A46">
+      <c r="R45" s="4">
+        <v>4</v>
+      </c>
+      <c r="S45" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="4">
         <v>7</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="4">
         <v>-88.39</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="4">
         <v>38.380000000000003</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="4">
         <v>48.436</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F46">
-        <v>12</v>
-      </c>
-      <c r="G46">
+      <c r="F46" s="4">
+        <v>12</v>
+      </c>
+      <c r="G46" s="4">
         <v>2008</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="4">
         <v>2004</v>
       </c>
-      <c r="J46">
-        <v>4</v>
-      </c>
-      <c r="K46">
+      <c r="J46" s="4">
+        <v>4</v>
+      </c>
+      <c r="K46" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N46">
-        <v>4</v>
-      </c>
-      <c r="O46">
+      <c r="N46" s="4">
+        <v>4</v>
+      </c>
+      <c r="O46" s="4">
         <v>15</v>
       </c>
-      <c r="P46">
-        <v>12</v>
-      </c>
-      <c r="Q46">
+      <c r="P46" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q46" s="4">
         <v>20081215</v>
       </c>
-      <c r="R46">
+      <c r="R46" s="4">
         <v>5</v>
       </c>
-      <c r="S46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A47">
+      <c r="S46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="4">
         <v>7</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="4">
         <v>-88.39</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="4">
         <v>38.380000000000003</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="4">
         <v>21.6</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F47">
-        <v>12</v>
-      </c>
-      <c r="G47">
+      <c r="F47" s="4">
+        <v>12</v>
+      </c>
+      <c r="G47" s="4">
         <v>2009</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="4">
         <v>2004</v>
       </c>
-      <c r="J47">
-        <v>4</v>
-      </c>
-      <c r="K47">
+      <c r="J47" s="4">
+        <v>4</v>
+      </c>
+      <c r="K47" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N47">
-        <v>4</v>
-      </c>
-      <c r="O47">
+      <c r="N47" s="4">
+        <v>4</v>
+      </c>
+      <c r="O47" s="4">
         <v>15</v>
       </c>
-      <c r="P47">
-        <v>12</v>
-      </c>
-      <c r="Q47">
+      <c r="P47" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q47" s="4">
         <v>20091215</v>
       </c>
-      <c r="R47">
+      <c r="R47" s="4">
         <v>6</v>
       </c>
-      <c r="S47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A48">
+      <c r="S47" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="4">
         <v>7</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="4">
         <v>-88.39</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="4">
         <v>38.380000000000003</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="4">
         <v>21.818000000000001</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F48">
-        <v>12</v>
-      </c>
-      <c r="G48">
+      <c r="F48" s="4">
+        <v>12</v>
+      </c>
+      <c r="G48" s="4">
         <v>2010</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="4">
         <v>2004</v>
       </c>
-      <c r="J48">
-        <v>4</v>
-      </c>
-      <c r="K48">
+      <c r="J48" s="4">
+        <v>4</v>
+      </c>
+      <c r="K48" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N48">
-        <v>4</v>
-      </c>
-      <c r="O48">
+      <c r="N48" s="4">
+        <v>4</v>
+      </c>
+      <c r="O48" s="4">
         <v>15</v>
       </c>
-      <c r="P48">
-        <v>12</v>
-      </c>
-      <c r="Q48">
+      <c r="P48" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="4">
         <v>20101215</v>
       </c>
-      <c r="R48">
+      <c r="R48" s="4">
         <v>7</v>
       </c>
-      <c r="S48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A49">
+      <c r="S48" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="4">
         <v>7</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="4">
         <v>-88.39</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="4">
         <v>38.380000000000003</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="4">
         <v>17.890999999999998</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F49">
-        <v>12</v>
-      </c>
-      <c r="G49">
+      <c r="F49" s="4">
+        <v>12</v>
+      </c>
+      <c r="G49" s="4">
         <v>2011</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="4">
         <v>2004</v>
       </c>
-      <c r="J49">
-        <v>4</v>
-      </c>
-      <c r="K49">
+      <c r="J49" s="4">
+        <v>4</v>
+      </c>
+      <c r="K49" s="4">
         <v>1.519999981</v>
       </c>
-      <c r="N49">
-        <v>4</v>
-      </c>
-      <c r="O49">
+      <c r="N49" s="4">
+        <v>4</v>
+      </c>
+      <c r="O49" s="4">
         <v>15</v>
       </c>
-      <c r="P49">
-        <v>12</v>
-      </c>
-      <c r="Q49">
+      <c r="P49" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q49" s="4">
         <v>20111215</v>
       </c>
-      <c r="R49">
+      <c r="R49" s="4">
         <v>8</v>
       </c>
-      <c r="S49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A50">
+      <c r="S49" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="5">
         <v>8</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="5">
         <v>-86.768904000000006</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="5">
         <v>36.760005999999997</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="5">
         <v>5.8</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="5">
         <v>18</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="5">
         <v>3</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="5">
         <v>2011</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="5">
         <v>2010</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J50">
-        <v>4</v>
-      </c>
-      <c r="K50">
+      <c r="J50" s="5">
+        <v>4</v>
+      </c>
+      <c r="K50" s="5">
         <v>1.458853245</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="N50">
-        <v>4</v>
-      </c>
-      <c r="O50">
+      <c r="N50" s="5">
+        <v>4</v>
+      </c>
+      <c r="O50" s="5">
         <v>18</v>
       </c>
-      <c r="P50">
+      <c r="P50" s="5">
         <v>3</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="5">
         <v>20110318</v>
       </c>
-      <c r="R50">
-        <v>1</v>
-      </c>
-      <c r="S50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A51">
+      <c r="R50" s="5">
+        <v>1</v>
+      </c>
+      <c r="S50" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="5">
         <v>8</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="5">
         <v>-86.768904000000006</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="5">
         <v>36.760005999999997</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="5">
         <v>12.2</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="5">
         <v>20</v>
       </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51">
+      <c r="F51" s="5">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5">
         <v>2012</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="5">
         <v>2010</v>
       </c>
-      <c r="J51">
-        <v>4</v>
-      </c>
-      <c r="K51">
+      <c r="J51" s="5">
+        <v>4</v>
+      </c>
+      <c r="K51" s="5">
         <v>1.458853245</v>
       </c>
-      <c r="N51">
-        <v>4</v>
-      </c>
-      <c r="O51">
+      <c r="N51" s="5">
+        <v>4</v>
+      </c>
+      <c r="O51" s="5">
         <v>20</v>
       </c>
-      <c r="P51">
-        <v>1</v>
-      </c>
-      <c r="Q51">
+      <c r="P51" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="5">
         <v>20120120</v>
       </c>
-      <c r="R51">
+      <c r="R51" s="5">
         <v>2</v>
       </c>
-      <c r="S51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A52">
+      <c r="S51" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
         <v>9</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="3">
         <v>-96.470219999999998</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="3">
         <v>41.248538000000003</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="3">
         <v>16.3</v>
       </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52">
-        <v>4</v>
-      </c>
-      <c r="G52">
+      <c r="E52" s="3">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3">
         <v>2010</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="3">
         <v>2008</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="3">
         <v>8</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="3">
         <v>1.514926553</v>
       </c>
-      <c r="L52" t="s">
+      <c r="L52" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="M52" t="s">
+      <c r="M52" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N52">
+      <c r="N52" s="3">
         <v>7</v>
       </c>
-      <c r="O52">
-        <v>1</v>
-      </c>
-      <c r="P52">
-        <v>4</v>
-      </c>
-      <c r="Q52">
+      <c r="O52" s="3">
+        <v>1</v>
+      </c>
+      <c r="P52" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3">
         <v>20100401</v>
       </c>
-      <c r="R52">
+      <c r="R52" s="3">
         <v>2</v>
       </c>
-      <c r="S52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A53">
+      <c r="S52" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
         <v>9</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="3">
         <v>-96.470219999999998</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="3">
         <v>41.248538000000003</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="3">
         <v>26.9</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="3">
         <v>2</v>
       </c>
-      <c r="F53">
-        <v>12</v>
-      </c>
-      <c r="G53">
+      <c r="F53" s="3">
+        <v>12</v>
+      </c>
+      <c r="G53" s="3">
         <v>2010</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="3">
         <v>2008</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="3">
         <v>8</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="3">
         <v>1.514926553</v>
       </c>
-      <c r="M53" t="s">
+      <c r="M53" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N53">
+      <c r="N53" s="3">
         <v>7</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="3">
         <v>2</v>
       </c>
-      <c r="P53">
-        <v>12</v>
-      </c>
-      <c r="Q53">
+      <c r="P53" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q53" s="3">
         <v>20101202</v>
       </c>
-      <c r="R53">
+      <c r="R53" s="3">
         <v>3</v>
       </c>
-      <c r="S53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A54">
+      <c r="S53" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
         <v>9</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="3">
         <v>-96.470219999999998</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="3">
         <v>41.248538000000003</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="3">
         <v>31.640544999999999</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="3">
         <v>29</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="3">
         <v>11</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <v>2011</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="3">
         <v>2008</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="3">
         <v>8</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="3">
         <v>1.514926553</v>
       </c>
-      <c r="M54" t="s">
+      <c r="M54" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N54">
+      <c r="N54" s="3">
         <v>7</v>
       </c>
-      <c r="O54">
+      <c r="O54" s="3">
         <v>29</v>
       </c>
-      <c r="P54">
+      <c r="P54" s="3">
         <v>11</v>
       </c>
-      <c r="Q54">
+      <c r="Q54" s="3">
         <v>20111129</v>
       </c>
-      <c r="R54">
-        <v>4</v>
-      </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A55">
+      <c r="R54" s="3">
+        <v>4</v>
+      </c>
+      <c r="S54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
         <v>9</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="3">
         <v>-96.470219999999998</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="3">
         <v>41.248538000000003</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="3">
         <v>23.940425000000001</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="3">
         <v>8</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="3">
         <v>11</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <v>2012</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="3">
         <v>2008</v>
       </c>
-      <c r="J55">
+      <c r="J55" s="3">
         <v>8</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="3">
         <v>1.514926553</v>
       </c>
-      <c r="M55" t="s">
+      <c r="M55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N55">
+      <c r="N55" s="3">
         <v>7</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="3">
         <v>8</v>
       </c>
-      <c r="P55">
+      <c r="P55" s="3">
         <v>11</v>
       </c>
-      <c r="Q55">
+      <c r="Q55" s="3">
         <v>20121108</v>
       </c>
-      <c r="R55">
+      <c r="R55" s="3">
         <v>5</v>
       </c>
-      <c r="S55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A56">
+      <c r="S55" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
         <v>9</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="3">
         <v>-96.470219999999998</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="3">
         <v>41.248538000000003</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="3">
         <v>18.2</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="3">
         <v>25</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="3">
         <v>11</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <v>2013</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="3">
         <v>2008</v>
       </c>
-      <c r="J56">
+      <c r="J56" s="3">
         <v>8</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="3">
         <v>1.514926553</v>
       </c>
-      <c r="M56" t="s">
+      <c r="M56" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N56">
+      <c r="N56" s="3">
         <v>7</v>
       </c>
-      <c r="O56">
+      <c r="O56" s="3">
         <v>25</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="3">
         <v>11</v>
       </c>
-      <c r="Q56">
+      <c r="Q56" s="3">
         <v>20131125</v>
       </c>
-      <c r="R56">
+      <c r="R56" s="3">
         <v>6</v>
       </c>
-      <c r="S56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A57">
+      <c r="S56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
         <v>9</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="3">
         <v>-96.470219999999998</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="3">
         <v>41.248538000000003</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="3">
         <v>16.399999999999999</v>
       </c>
-      <c r="E57">
-        <v>12</v>
-      </c>
-      <c r="F57">
-        <v>12</v>
-      </c>
-      <c r="G57">
+      <c r="E57" s="3">
+        <v>12</v>
+      </c>
+      <c r="F57" s="3">
+        <v>12</v>
+      </c>
+      <c r="G57" s="3">
         <v>2014</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="3">
         <v>2008</v>
       </c>
-      <c r="J57">
+      <c r="J57" s="3">
         <v>8</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="3">
         <v>1.514926553</v>
       </c>
-      <c r="M57" t="s">
+      <c r="M57" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N57">
+      <c r="N57" s="3">
         <v>7</v>
       </c>
-      <c r="O57">
-        <v>12</v>
-      </c>
-      <c r="P57">
-        <v>12</v>
-      </c>
-      <c r="Q57">
+      <c r="O57" s="3">
+        <v>12</v>
+      </c>
+      <c r="P57" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q57" s="3">
         <v>20141212</v>
       </c>
-      <c r="R57">
+      <c r="R57" s="3">
         <v>7</v>
       </c>
-      <c r="S57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A58">
+      <c r="S57" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
         <v>9</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="3">
         <v>-96.470219999999998</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="3">
         <v>41.248538000000003</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="3">
         <v>27.8</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="3">
         <v>10</v>
       </c>
-      <c r="F58">
-        <v>12</v>
-      </c>
-      <c r="G58">
+      <c r="F58" s="3">
+        <v>12</v>
+      </c>
+      <c r="G58" s="3">
         <v>2015</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="3">
         <v>2008</v>
       </c>
-      <c r="J58">
+      <c r="J58" s="3">
         <v>8</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="3">
         <v>1.514926553</v>
       </c>
-      <c r="M58" t="s">
+      <c r="M58" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N58">
+      <c r="N58" s="3">
         <v>7</v>
       </c>
-      <c r="O58">
+      <c r="O58" s="3">
         <v>10</v>
       </c>
-      <c r="P58">
-        <v>12</v>
-      </c>
-      <c r="Q58">
+      <c r="P58" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q58" s="3">
         <v>20151210</v>
       </c>
-      <c r="R58">
+      <c r="R58" s="3">
         <v>8</v>
       </c>
-      <c r="S58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A59">
+      <c r="S58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3">
         <v>10</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="3">
         <v>-84.504194999999996</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="3">
         <v>38.030633999999999</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="3">
         <v>16.8</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="3">
         <v>9</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="3">
         <v>3</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <v>2010</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="3">
         <v>2008</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J59" s="1">
-        <v>4</v>
-      </c>
-      <c r="K59">
+      <c r="J59" s="3">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>1.1601849790000001</v>
       </c>
-      <c r="M59" t="s">
+      <c r="M59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N59">
-        <v>4</v>
-      </c>
-      <c r="O59">
+      <c r="N59" s="3">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>9</v>
       </c>
-      <c r="P59">
+      <c r="P59" s="3">
         <v>3</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="3">
         <v>20100309</v>
       </c>
-      <c r="R59">
+      <c r="R59" s="3">
         <v>2</v>
       </c>
-      <c r="S59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A60">
+      <c r="S59" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="3">
         <v>10</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="3">
         <v>-84.504194999999996</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="3">
         <v>38.030633999999999</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="3">
         <v>12.1</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="3">
         <v>11</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="3">
         <v>11</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <v>2010</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="3">
         <v>2008</v>
       </c>
-      <c r="J60" s="1">
-        <v>4</v>
-      </c>
-      <c r="K60">
+      <c r="J60" s="3">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>1.1601849790000001</v>
       </c>
-      <c r="M60" t="s">
+      <c r="M60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N60">
-        <v>4</v>
-      </c>
-      <c r="O60">
+      <c r="N60" s="3">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>11</v>
       </c>
-      <c r="P60">
+      <c r="P60" s="3">
         <v>11</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="3">
         <v>20101111</v>
       </c>
-      <c r="R60">
+      <c r="R60" s="3">
         <v>3</v>
       </c>
-      <c r="S60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A61">
+      <c r="S60" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="3">
         <v>10</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="3">
         <v>-84.504194999999996</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="3">
         <v>38.030633999999999</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="3">
         <v>19.3</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="3">
         <v>19</v>
       </c>
-      <c r="F61">
-        <v>12</v>
-      </c>
-      <c r="G61">
+      <c r="F61" s="3">
+        <v>12</v>
+      </c>
+      <c r="G61" s="3">
         <v>2011</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="3">
         <v>2008</v>
       </c>
-      <c r="J61" s="1">
-        <v>4</v>
-      </c>
-      <c r="K61">
+      <c r="J61" s="3">
+        <v>4</v>
+      </c>
+      <c r="K61" s="3">
         <v>1.1601849790000001</v>
       </c>
-      <c r="M61" t="s">
+      <c r="M61" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N61">
-        <v>4</v>
-      </c>
-      <c r="O61">
+      <c r="N61" s="3">
+        <v>4</v>
+      </c>
+      <c r="O61" s="3">
         <v>19</v>
       </c>
-      <c r="P61">
-        <v>12</v>
-      </c>
-      <c r="Q61">
+      <c r="P61" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q61" s="3">
         <v>20111219</v>
       </c>
-      <c r="R61">
-        <v>4</v>
-      </c>
-      <c r="S61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A62">
+      <c r="R61" s="3">
+        <v>4</v>
+      </c>
+      <c r="S61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="3">
         <v>10</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="3">
         <v>-84.504194999999996</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="3">
         <v>38.030633999999999</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="3">
         <v>12.7</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="3">
         <v>18</v>
       </c>
-      <c r="F62">
-        <v>12</v>
-      </c>
-      <c r="G62">
+      <c r="F62" s="3">
+        <v>12</v>
+      </c>
+      <c r="G62" s="3">
         <v>2012</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="3">
         <v>2008</v>
       </c>
-      <c r="J62" s="1">
-        <v>4</v>
-      </c>
-      <c r="K62">
+      <c r="J62" s="3">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>1.1601849790000001</v>
       </c>
-      <c r="M62" t="s">
+      <c r="M62" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N62">
-        <v>4</v>
-      </c>
-      <c r="O62">
+      <c r="N62" s="3">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>18</v>
       </c>
-      <c r="P62">
-        <v>12</v>
-      </c>
-      <c r="Q62">
+      <c r="P62" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q62" s="3">
         <v>20121218</v>
       </c>
-      <c r="R62">
+      <c r="R62" s="3">
         <v>5</v>
       </c>
-      <c r="S62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A63">
+      <c r="S62" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
         <v>10</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="3">
         <v>-84.504194999999996</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="3">
         <v>38.030633999999999</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="3">
         <v>19.2</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="3">
         <v>19</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="3">
         <v>3</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="3">
         <v>2014</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="3">
         <v>2008</v>
       </c>
-      <c r="J63" s="1">
-        <v>4</v>
-      </c>
-      <c r="K63">
+      <c r="J63" s="3">
+        <v>4</v>
+      </c>
+      <c r="K63" s="3">
         <v>1.1601849790000001</v>
       </c>
-      <c r="M63" t="s">
+      <c r="M63" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N63">
-        <v>4</v>
-      </c>
-      <c r="O63">
+      <c r="N63" s="3">
+        <v>4</v>
+      </c>
+      <c r="O63" s="3">
         <v>19</v>
       </c>
-      <c r="P63">
+      <c r="P63" s="3">
         <v>3</v>
       </c>
-      <c r="Q63">
+      <c r="Q63" s="3">
         <v>20140319</v>
       </c>
-      <c r="R63">
+      <c r="R63" s="3">
         <v>6</v>
       </c>
-      <c r="S63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A64">
+      <c r="S63" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
         <v>10</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="3">
         <v>-84.504194999999996</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="3">
         <v>38.030633999999999</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="3">
         <v>13</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="3">
         <v>17</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="3">
         <v>3</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="3">
         <v>2015</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="3">
         <v>2008</v>
       </c>
-      <c r="J64" s="1">
-        <v>4</v>
-      </c>
-      <c r="K64">
+      <c r="J64" s="3">
+        <v>4</v>
+      </c>
+      <c r="K64" s="3">
         <v>1.1601849790000001</v>
       </c>
-      <c r="M64" t="s">
+      <c r="M64" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N64">
-        <v>4</v>
-      </c>
-      <c r="O64">
+      <c r="N64" s="3">
+        <v>4</v>
+      </c>
+      <c r="O64" s="3">
         <v>17</v>
       </c>
-      <c r="P64">
+      <c r="P64" s="3">
         <v>3</v>
       </c>
-      <c r="Q64">
+      <c r="Q64" s="3">
         <v>20150317</v>
       </c>
-      <c r="R64">
+      <c r="R64" s="3">
         <v>7</v>
       </c>
-      <c r="S64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A65">
+      <c r="S64" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3">
         <v>10</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="3">
         <v>-84.504194999999996</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="3">
         <v>38.030633999999999</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="3">
         <v>18.3</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="3">
         <v>18</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="3">
         <v>3</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="3">
         <v>2016</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="3">
         <v>2008</v>
       </c>
-      <c r="J65" s="1">
-        <v>4</v>
-      </c>
-      <c r="K65">
+      <c r="J65" s="3">
+        <v>4</v>
+      </c>
+      <c r="K65" s="3">
         <v>1.1601849790000001</v>
       </c>
-      <c r="M65" t="s">
+      <c r="M65" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N65">
-        <v>4</v>
-      </c>
-      <c r="O65">
+      <c r="N65" s="3">
+        <v>4</v>
+      </c>
+      <c r="O65" s="3">
         <v>18</v>
       </c>
-      <c r="P65">
+      <c r="P65" s="3">
         <v>3</v>
       </c>
-      <c r="Q65">
+      <c r="Q65" s="3">
         <v>20160318</v>
       </c>
-      <c r="R65">
+      <c r="R65" s="3">
         <v>8</v>
       </c>
-      <c r="S65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A66">
+      <c r="S65" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3">
         <v>11</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="3">
         <v>-88.227204</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="3">
         <v>40.102133000000002</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="3">
         <v>1.8</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="3">
         <v>17</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="3">
         <v>2</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="3">
         <v>2010</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="3">
         <v>2008</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J66" s="1">
-        <v>4</v>
-      </c>
-      <c r="K66">
+      <c r="J66" s="3">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>1.519999981</v>
       </c>
-      <c r="M66" t="s">
+      <c r="M66" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N66">
-        <v>4</v>
-      </c>
-      <c r="O66">
+      <c r="N66" s="3">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>17</v>
       </c>
-      <c r="P66">
+      <c r="P66" s="3">
         <v>2</v>
       </c>
-      <c r="Q66">
+      <c r="Q66" s="3">
         <v>20100217</v>
       </c>
-      <c r="R66">
+      <c r="R66" s="3">
         <v>2</v>
       </c>
-      <c r="S66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A67">
+      <c r="S66" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
         <v>11</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="3">
         <v>-88.227204</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="3">
         <v>40.102133000000002</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="3">
         <v>14.8</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="3">
         <v>29</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="3">
         <v>11</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="3">
         <v>2010</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="3">
         <v>2008</v>
       </c>
-      <c r="J67" s="1">
-        <v>4</v>
-      </c>
-      <c r="K67">
+      <c r="J67" s="3">
+        <v>4</v>
+      </c>
+      <c r="K67" s="3">
         <v>1.519999981</v>
       </c>
-      <c r="M67" t="s">
+      <c r="M67" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N67">
-        <v>4</v>
-      </c>
-      <c r="O67">
+      <c r="N67" s="3">
+        <v>4</v>
+      </c>
+      <c r="O67" s="3">
         <v>29</v>
       </c>
-      <c r="P67">
+      <c r="P67" s="3">
         <v>11</v>
       </c>
-      <c r="Q67">
+      <c r="Q67" s="3">
         <v>20101129</v>
       </c>
-      <c r="R67">
+      <c r="R67" s="3">
         <v>3</v>
       </c>
-      <c r="S67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A68">
+      <c r="S67" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
         <v>11</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="3">
         <v>-88.227204</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="3">
         <v>40.102133000000002</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="3">
         <v>17.3</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="3">
         <v>6</v>
       </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68">
+      <c r="F68" s="3">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3">
         <v>2012</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="3">
         <v>2008</v>
       </c>
-      <c r="J68" s="1">
-        <v>4</v>
-      </c>
-      <c r="K68">
+      <c r="J68" s="3">
+        <v>4</v>
+      </c>
+      <c r="K68" s="3">
         <v>1.519999981</v>
       </c>
-      <c r="M68" t="s">
+      <c r="M68" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N68">
-        <v>4</v>
-      </c>
-      <c r="O68">
+      <c r="N68" s="3">
+        <v>4</v>
+      </c>
+      <c r="O68" s="3">
         <v>6</v>
       </c>
-      <c r="P68">
-        <v>1</v>
-      </c>
-      <c r="Q68">
+      <c r="P68" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="3">
         <v>20120106</v>
       </c>
-      <c r="R68">
-        <v>4</v>
-      </c>
-      <c r="S68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A69">
+      <c r="R68" s="3">
+        <v>4</v>
+      </c>
+      <c r="S68" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
         <v>11</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="3">
         <v>-88.227204</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="3">
         <v>40.102133000000002</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="3">
         <v>5.8</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="3">
         <v>8</v>
       </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69">
+      <c r="F69" s="3">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3">
         <v>2013</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="3">
         <v>2008</v>
       </c>
-      <c r="J69" s="1">
-        <v>4</v>
-      </c>
-      <c r="K69">
+      <c r="J69" s="3">
+        <v>4</v>
+      </c>
+      <c r="K69" s="3">
         <v>1.519999981</v>
       </c>
-      <c r="M69" t="s">
+      <c r="M69" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N69">
-        <v>4</v>
-      </c>
-      <c r="O69">
+      <c r="N69" s="3">
+        <v>4</v>
+      </c>
+      <c r="O69" s="3">
         <v>8</v>
       </c>
-      <c r="P69">
-        <v>1</v>
-      </c>
-      <c r="Q69">
+      <c r="P69" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="3">
         <v>20130108</v>
       </c>
-      <c r="R69">
+      <c r="R69" s="3">
         <v>5</v>
       </c>
-      <c r="S69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A70">
+      <c r="S69" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
         <v>11</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="3">
         <v>-88.227204</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="3">
         <v>40.102133000000002</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="3">
         <v>15.3</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="3">
         <v>30</v>
       </c>
-      <c r="F70">
-        <v>12</v>
-      </c>
-      <c r="G70">
+      <c r="F70" s="3">
+        <v>12</v>
+      </c>
+      <c r="G70" s="3">
         <v>2013</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="3">
         <v>2008</v>
       </c>
-      <c r="J70" s="1">
-        <v>4</v>
-      </c>
-      <c r="K70">
+      <c r="J70" s="3">
+        <v>4</v>
+      </c>
+      <c r="K70" s="3">
         <v>1.519999981</v>
       </c>
-      <c r="M70" t="s">
+      <c r="M70" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N70">
-        <v>4</v>
-      </c>
-      <c r="O70">
+      <c r="N70" s="3">
+        <v>4</v>
+      </c>
+      <c r="O70" s="3">
         <v>30</v>
       </c>
-      <c r="P70">
-        <v>12</v>
-      </c>
-      <c r="Q70">
+      <c r="P70" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q70" s="3">
         <v>20131230</v>
       </c>
-      <c r="R70">
+      <c r="R70" s="3">
         <v>6</v>
       </c>
-      <c r="S70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A71">
+      <c r="S70" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
         <v>11</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="3">
         <v>-88.227204</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="3">
         <v>40.102133000000002</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="3">
         <v>8.5</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="3">
         <v>30</v>
       </c>
-      <c r="F71">
-        <v>12</v>
-      </c>
-      <c r="G71">
+      <c r="F71" s="3">
+        <v>12</v>
+      </c>
+      <c r="G71" s="3">
         <v>2014</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="3">
         <v>2008</v>
       </c>
-      <c r="J71" s="1">
-        <v>4</v>
-      </c>
-      <c r="K71">
+      <c r="J71" s="3">
+        <v>4</v>
+      </c>
+      <c r="K71" s="3">
         <v>1.519999981</v>
       </c>
-      <c r="M71" t="s">
+      <c r="M71" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N71">
-        <v>4</v>
-      </c>
-      <c r="O71">
+      <c r="N71" s="3">
+        <v>4</v>
+      </c>
+      <c r="O71" s="3">
         <v>30</v>
       </c>
-      <c r="P71">
-        <v>12</v>
-      </c>
-      <c r="Q71">
+      <c r="P71" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q71" s="3">
         <v>20141230</v>
       </c>
-      <c r="R71">
+      <c r="R71" s="3">
         <v>7</v>
       </c>
-      <c r="S71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A72">
+      <c r="S71" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
         <v>11</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="3">
         <v>-88.227204</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="3">
         <v>40.102133000000002</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="3">
         <v>16.600000000000001</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="3">
         <v>21</v>
       </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72">
+      <c r="F72" s="3">
+        <v>1</v>
+      </c>
+      <c r="G72" s="3">
         <v>2016</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="3">
         <v>2008</v>
       </c>
-      <c r="J72" s="1">
-        <v>4</v>
-      </c>
-      <c r="K72">
+      <c r="J72" s="3">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>1.519999981</v>
       </c>
-      <c r="M72" t="s">
+      <c r="M72" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N72">
-        <v>4</v>
-      </c>
-      <c r="O72">
+      <c r="N72" s="3">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>21</v>
       </c>
-      <c r="P72">
-        <v>1</v>
-      </c>
-      <c r="Q72">
+      <c r="P72" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="3">
         <v>20160121</v>
       </c>
-      <c r="R72">
+      <c r="R72" s="3">
         <v>8</v>
       </c>
-      <c r="S72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>12</v>
-      </c>
-      <c r="B73">
+      <c r="S72" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="3">
+        <v>12</v>
+      </c>
+      <c r="B73" s="3">
         <v>-74.244632999999993</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="3">
         <v>40.215611000000003</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="3">
         <v>11.1</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="3">
         <v>16</v>
       </c>
-      <c r="F73">
-        <v>12</v>
-      </c>
-      <c r="G73">
+      <c r="F73" s="3">
+        <v>12</v>
+      </c>
+      <c r="G73" s="3">
         <v>2009</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="3">
         <v>2008</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I73" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J73">
-        <v>1</v>
-      </c>
-      <c r="K73">
+      <c r="J73" s="3">
+        <v>1</v>
+      </c>
+      <c r="K73" s="3">
         <v>1.4932649140000001</v>
       </c>
-      <c r="M73" t="s">
+      <c r="M73" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N73">
+      <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73">
+      <c r="O73" s="3">
         <v>16</v>
       </c>
-      <c r="P73">
-        <v>12</v>
-      </c>
-      <c r="Q73">
+      <c r="P73" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q73" s="3">
         <v>20091216</v>
       </c>
-      <c r="R73">
+      <c r="R73" s="3">
         <v>2</v>
       </c>
-      <c r="S73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>12</v>
-      </c>
-      <c r="B74">
+      <c r="S73" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
+        <v>12</v>
+      </c>
+      <c r="B74" s="3">
         <v>-74.244632999999993</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="3">
         <v>40.215611000000003</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="3">
         <v>12.4</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="3">
         <v>9</v>
       </c>
-      <c r="F74">
-        <v>12</v>
-      </c>
-      <c r="G74">
+      <c r="F74" s="3">
+        <v>12</v>
+      </c>
+      <c r="G74" s="3">
         <v>2010</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="3">
         <v>2008</v>
       </c>
-      <c r="J74">
-        <v>1</v>
-      </c>
-      <c r="K74">
+      <c r="J74" s="3">
+        <v>1</v>
+      </c>
+      <c r="K74" s="3">
         <v>1.4932649140000001</v>
       </c>
-      <c r="M74" t="s">
+      <c r="M74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N74">
+      <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74">
+      <c r="O74" s="3">
         <v>9</v>
       </c>
-      <c r="P74">
-        <v>12</v>
-      </c>
-      <c r="Q74">
+      <c r="P74" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q74" s="3">
         <v>20101209</v>
       </c>
-      <c r="R74">
+      <c r="R74" s="3">
         <v>3</v>
       </c>
-      <c r="S74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <v>12</v>
-      </c>
-      <c r="B75">
+      <c r="S74" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
+        <v>12</v>
+      </c>
+      <c r="B75" s="3">
         <v>-74.244632999999993</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="3">
         <v>40.215611000000003</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="3">
         <v>18.8</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="3">
         <v>14</v>
       </c>
-      <c r="F75">
-        <v>12</v>
-      </c>
-      <c r="G75">
+      <c r="F75" s="3">
+        <v>12</v>
+      </c>
+      <c r="G75" s="3">
         <v>2011</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="3">
         <v>2008</v>
       </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="K75">
+      <c r="J75" s="3">
+        <v>1</v>
+      </c>
+      <c r="K75" s="3">
         <v>1.4932649140000001</v>
       </c>
-      <c r="M75" t="s">
+      <c r="M75" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N75">
+      <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75">
+      <c r="O75" s="3">
         <v>14</v>
       </c>
-      <c r="P75">
-        <v>12</v>
-      </c>
-      <c r="Q75">
+      <c r="P75" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q75" s="3">
         <v>20111214</v>
       </c>
-      <c r="R75">
-        <v>4</v>
-      </c>
-      <c r="S75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A76">
-        <v>12</v>
-      </c>
-      <c r="B76">
+      <c r="R75" s="3">
+        <v>4</v>
+      </c>
+      <c r="S75" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
+        <v>12</v>
+      </c>
+      <c r="B76" s="3">
         <v>-74.244632999999993</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="3">
         <v>40.215611000000003</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="3">
         <v>14</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="3">
         <v>7</v>
       </c>
-      <c r="F76">
-        <v>12</v>
-      </c>
-      <c r="G76">
+      <c r="F76" s="3">
+        <v>12</v>
+      </c>
+      <c r="G76" s="3">
         <v>2012</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="3">
         <v>2008</v>
       </c>
-      <c r="J76">
-        <v>1</v>
-      </c>
-      <c r="K76">
+      <c r="J76" s="3">
+        <v>1</v>
+      </c>
+      <c r="K76" s="3">
         <v>1.4932649140000001</v>
       </c>
-      <c r="M76" t="s">
+      <c r="M76" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N76">
+      <c r="N76" s="3">
         <v>0</v>
       </c>
-      <c r="O76">
+      <c r="O76" s="3">
         <v>7</v>
       </c>
-      <c r="P76">
-        <v>12</v>
-      </c>
-      <c r="Q76">
+      <c r="P76" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q76" s="3">
         <v>20121207</v>
       </c>
-      <c r="R76">
+      <c r="R76" s="3">
         <v>5</v>
       </c>
-      <c r="S76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>12</v>
-      </c>
-      <c r="B77">
+      <c r="S76" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
+        <v>12</v>
+      </c>
+      <c r="B77" s="3">
         <v>-74.244632999999993</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="3">
         <v>40.215611000000003</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="3">
         <v>18.7</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="3">
         <v>10</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="3">
         <v>3</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="3">
         <v>2014</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="3">
         <v>2008</v>
       </c>
-      <c r="J77">
-        <v>1</v>
-      </c>
-      <c r="K77">
+      <c r="J77" s="3">
+        <v>1</v>
+      </c>
+      <c r="K77" s="3">
         <v>1.4932649140000001</v>
       </c>
-      <c r="M77" t="s">
+      <c r="M77" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N77">
+      <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77">
+      <c r="O77" s="3">
         <v>10</v>
       </c>
-      <c r="P77">
+      <c r="P77" s="3">
         <v>3</v>
       </c>
-      <c r="Q77">
+      <c r="Q77" s="3">
         <v>20140310</v>
       </c>
-      <c r="R77">
+      <c r="R77" s="3">
         <v>6</v>
       </c>
-      <c r="S77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>12</v>
-      </c>
-      <c r="B78">
+      <c r="S77" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="3">
+        <v>12</v>
+      </c>
+      <c r="B78" s="3">
         <v>-74.244632999999993</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="3">
         <v>40.215611000000003</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="3">
         <v>14.7</v>
       </c>
-      <c r="E78">
-        <v>1</v>
-      </c>
-      <c r="F78">
-        <v>12</v>
-      </c>
-      <c r="G78">
+      <c r="E78" s="3">
+        <v>1</v>
+      </c>
+      <c r="F78" s="3">
+        <v>12</v>
+      </c>
+      <c r="G78" s="3">
         <v>2014</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="3">
         <v>2008</v>
       </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
-      <c r="K78">
+      <c r="J78" s="3">
+        <v>1</v>
+      </c>
+      <c r="K78" s="3">
         <v>1.4932649140000001</v>
       </c>
-      <c r="M78" t="s">
+      <c r="M78" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N78">
+      <c r="N78" s="3">
         <v>0</v>
       </c>
-      <c r="O78">
-        <v>1</v>
-      </c>
-      <c r="P78">
-        <v>12</v>
-      </c>
-      <c r="Q78">
+      <c r="O78" s="3">
+        <v>1</v>
+      </c>
+      <c r="P78" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q78" s="3">
         <v>20141201</v>
       </c>
-      <c r="R78">
+      <c r="R78" s="3">
         <v>7</v>
       </c>
-      <c r="S78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>12</v>
-      </c>
-      <c r="B79">
+      <c r="S78" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
+        <v>12</v>
+      </c>
+      <c r="B79" s="3">
         <v>-74.244632999999993</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="3">
         <v>40.215611000000003</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="3">
         <v>20</v>
       </c>
-      <c r="E79">
-        <v>12</v>
-      </c>
-      <c r="F79">
-        <v>1</v>
-      </c>
-      <c r="G79">
+      <c r="E79" s="3">
+        <v>12</v>
+      </c>
+      <c r="F79" s="3">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3">
         <v>2016</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="3">
         <v>2008</v>
       </c>
-      <c r="J79">
-        <v>1</v>
-      </c>
-      <c r="K79">
+      <c r="J79" s="3">
+        <v>1</v>
+      </c>
+      <c r="K79" s="3">
         <v>1.4932649140000001</v>
       </c>
-      <c r="M79" t="s">
+      <c r="M79" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N79">
+      <c r="N79" s="3">
         <v>0</v>
       </c>
-      <c r="O79">
-        <v>12</v>
-      </c>
-      <c r="P79">
-        <v>1</v>
-      </c>
-      <c r="Q79">
+      <c r="O79" s="3">
+        <v>12</v>
+      </c>
+      <c r="P79" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="3">
         <v>20160112</v>
       </c>
-      <c r="R79">
+      <c r="R79" s="3">
         <v>8</v>
       </c>
-      <c r="S79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A80">
+      <c r="S79" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="3">
         <v>13</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="3">
         <v>-79.370071999999993</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="3">
         <v>36.957695000000001</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="3">
         <v>8.4</v>
       </c>
-      <c r="E80">
-        <v>12</v>
-      </c>
-      <c r="F80">
-        <v>12</v>
-      </c>
-      <c r="G80">
+      <c r="E80" s="3">
+        <v>12</v>
+      </c>
+      <c r="F80" s="3">
+        <v>12</v>
+      </c>
+      <c r="G80" s="3">
         <v>2011</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="3">
         <v>2010</v>
       </c>
-      <c r="I80" t="s">
+      <c r="I80" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J80">
+      <c r="J80" s="3">
         <v>3</v>
       </c>
-      <c r="K80">
+      <c r="K80" s="3">
         <v>1.3947854040000001</v>
       </c>
-      <c r="M80" t="s">
+      <c r="M80" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N80">
+      <c r="N80" s="3">
         <v>2</v>
       </c>
-      <c r="O80">
-        <v>12</v>
-      </c>
-      <c r="P80">
-        <v>12</v>
-      </c>
-      <c r="Q80">
+      <c r="O80" s="3">
+        <v>12</v>
+      </c>
+      <c r="P80" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q80" s="3">
         <v>20111212</v>
       </c>
-      <c r="R80">
+      <c r="R80" s="3">
         <v>2</v>
       </c>
-      <c r="S80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A81">
+      <c r="S80" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
         <v>13</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="3">
         <v>-79.370071999999993</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="3">
         <v>36.957695000000001</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="3">
         <v>16.3</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="3">
         <v>15</v>
       </c>
-      <c r="F81">
-        <v>12</v>
-      </c>
-      <c r="G81">
+      <c r="F81" s="3">
+        <v>12</v>
+      </c>
+      <c r="G81" s="3">
         <v>2012</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="3">
         <v>2010</v>
       </c>
-      <c r="J81">
+      <c r="J81" s="3">
         <v>3</v>
       </c>
-      <c r="K81">
+      <c r="K81" s="3">
         <v>1.3947854040000001</v>
       </c>
-      <c r="M81" t="s">
+      <c r="M81" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N81">
+      <c r="N81" s="3">
         <v>2</v>
       </c>
-      <c r="O81">
+      <c r="O81" s="3">
         <v>15</v>
       </c>
-      <c r="P81">
-        <v>12</v>
-      </c>
-      <c r="Q81">
+      <c r="P81" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q81" s="3">
         <v>20121215</v>
       </c>
-      <c r="R81">
+      <c r="R81" s="3">
         <v>3</v>
       </c>
-      <c r="S81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A82">
+      <c r="S81" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
         <v>13</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="3">
         <v>-79.370071999999993</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="3">
         <v>36.957695000000001</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="3">
         <v>14.4</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="3">
         <v>18</v>
       </c>
-      <c r="F82">
-        <v>12</v>
-      </c>
-      <c r="G82">
+      <c r="F82" s="3">
+        <v>12</v>
+      </c>
+      <c r="G82" s="3">
         <v>2013</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="3">
         <v>2010</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="3">
         <v>3</v>
       </c>
-      <c r="K82">
+      <c r="K82" s="3">
         <v>1.3947854040000001</v>
       </c>
-      <c r="M82" t="s">
+      <c r="M82" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N82">
+      <c r="N82" s="3">
         <v>2</v>
       </c>
-      <c r="O82">
+      <c r="O82" s="3">
         <v>18</v>
       </c>
-      <c r="P82">
-        <v>12</v>
-      </c>
-      <c r="Q82">
+      <c r="P82" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q82" s="3">
         <v>20131218</v>
       </c>
-      <c r="R82">
-        <v>4</v>
-      </c>
-      <c r="S82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A83">
+      <c r="R82" s="3">
+        <v>4</v>
+      </c>
+      <c r="S82" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
         <v>13</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="3">
         <v>-79.370071999999993</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="3">
         <v>36.957695000000001</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="3">
         <v>13.6</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="3">
         <v>18</v>
       </c>
-      <c r="F83">
-        <v>12</v>
-      </c>
-      <c r="G83">
+      <c r="F83" s="3">
+        <v>12</v>
+      </c>
+      <c r="G83" s="3">
         <v>2014</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="3">
         <v>2010</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="3">
         <v>3</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="3">
         <v>1.3947854040000001</v>
       </c>
-      <c r="M83" t="s">
+      <c r="M83" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N83">
+      <c r="N83" s="3">
         <v>2</v>
       </c>
-      <c r="O83">
+      <c r="O83" s="3">
         <v>18</v>
       </c>
-      <c r="P83">
-        <v>12</v>
-      </c>
-      <c r="Q83">
+      <c r="P83" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q83" s="3">
         <v>20141218</v>
       </c>
-      <c r="R83">
+      <c r="R83" s="3">
         <v>5</v>
       </c>
-      <c r="S83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A84">
+      <c r="S83" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="3">
         <v>13</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="3">
         <v>-79.370071999999993</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="3">
         <v>36.957695000000001</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="3">
         <v>12.5</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="3">
         <v>15</v>
       </c>
-      <c r="F84">
-        <v>12</v>
-      </c>
-      <c r="G84">
+      <c r="F84" s="3">
+        <v>12</v>
+      </c>
+      <c r="G84" s="3">
         <v>2015</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="3">
         <v>2010</v>
       </c>
-      <c r="J84">
+      <c r="J84" s="3">
         <v>3</v>
       </c>
-      <c r="K84">
+      <c r="K84" s="3">
         <v>1.3947854040000001</v>
       </c>
-      <c r="M84" t="s">
+      <c r="M84" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N84">
+      <c r="N84" s="3">
         <v>2</v>
       </c>
-      <c r="O84">
+      <c r="O84" s="3">
         <v>15</v>
       </c>
-      <c r="P84">
-        <v>12</v>
-      </c>
-      <c r="Q84">
+      <c r="P84" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q84" s="3">
         <v>20151215</v>
       </c>
-      <c r="R84">
+      <c r="R84" s="3">
         <v>6</v>
       </c>
-      <c r="S84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A85">
+      <c r="S84" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
         <v>14</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="2">
         <v>-96.583299999999994</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="2">
         <v>39.183300000000003</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="2">
         <v>11.8</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="2">
         <v>23</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="2">
         <v>11</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="2">
         <v>2008</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="2">
         <v>2007</v>
       </c>
-      <c r="J85">
+      <c r="J85" s="2">
         <v>8</v>
       </c>
-      <c r="K85">
+      <c r="K85" s="2">
         <v>1.098957062</v>
       </c>
-      <c r="L85" t="s">
+      <c r="L85" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N85">
+      <c r="N85" s="2">
         <v>7</v>
       </c>
-      <c r="O85">
+      <c r="O85" s="2">
         <v>23</v>
       </c>
-      <c r="P85">
+      <c r="P85" s="2">
         <v>11</v>
       </c>
-      <c r="Q85">
+      <c r="Q85" s="2">
         <v>20081123</v>
       </c>
-      <c r="R85">
+      <c r="R85" s="2">
         <v>2</v>
       </c>
-      <c r="S85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A86">
+      <c r="S85" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
         <v>14</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="2">
         <v>-96.583299999999994</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="2">
         <v>39.183300000000003</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="2">
         <v>12.1</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="2">
         <v>2</v>
       </c>
-      <c r="F86">
-        <v>12</v>
-      </c>
-      <c r="G86">
+      <c r="F86" s="2">
+        <v>12</v>
+      </c>
+      <c r="G86" s="2">
         <v>2009</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="2">
         <v>2007</v>
       </c>
-      <c r="J86">
+      <c r="J86" s="2">
         <v>8</v>
       </c>
-      <c r="K86">
+      <c r="K86" s="2">
         <v>1.098957062</v>
       </c>
-      <c r="N86">
+      <c r="N86" s="2">
         <v>7</v>
       </c>
-      <c r="O86">
+      <c r="O86" s="2">
         <v>2</v>
       </c>
-      <c r="P86">
-        <v>12</v>
-      </c>
-      <c r="Q86">
+      <c r="P86" s="2">
+        <v>12</v>
+      </c>
+      <c r="Q86" s="2">
         <v>20091202</v>
       </c>
-      <c r="R86">
+      <c r="R86" s="2">
         <v>3</v>
       </c>
-      <c r="S86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A87">
+      <c r="S86" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
         <v>14</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="2">
         <v>-96.583299999999994</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="2">
         <v>39.183300000000003</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="2">
         <v>9.6999999999999993</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="2">
         <v>2</v>
       </c>
-      <c r="F87">
-        <v>12</v>
-      </c>
-      <c r="G87">
+      <c r="F87" s="2">
+        <v>12</v>
+      </c>
+      <c r="G87" s="2">
         <v>2010</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="2">
         <v>2007</v>
       </c>
-      <c r="J87">
+      <c r="J87" s="2">
         <v>8</v>
       </c>
-      <c r="K87">
+      <c r="K87" s="2">
         <v>1.098957062</v>
       </c>
-      <c r="N87">
+      <c r="N87" s="2">
         <v>7</v>
       </c>
-      <c r="O87">
+      <c r="O87" s="2">
         <v>2</v>
       </c>
-      <c r="P87">
-        <v>12</v>
-      </c>
-      <c r="Q87">
+      <c r="P87" s="2">
+        <v>12</v>
+      </c>
+      <c r="Q87" s="2">
         <v>20101202</v>
       </c>
-      <c r="R87">
-        <v>4</v>
-      </c>
-      <c r="S87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A88">
+      <c r="R87" s="2">
+        <v>4</v>
+      </c>
+      <c r="S87" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
         <v>14</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="2">
         <v>-96.583299999999994</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="2">
         <v>39.183300000000003</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="2">
         <v>17.8</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="2">
         <v>6</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="2">
         <v>11</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="2">
         <v>2011</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="2">
         <v>2007</v>
       </c>
-      <c r="J88">
+      <c r="J88" s="2">
         <v>8</v>
       </c>
-      <c r="K88">
+      <c r="K88" s="2">
         <v>1.098957062</v>
       </c>
-      <c r="N88">
+      <c r="N88" s="2">
         <v>7</v>
       </c>
-      <c r="O88">
+      <c r="O88" s="2">
         <v>6</v>
       </c>
-      <c r="P88">
+      <c r="P88" s="2">
         <v>11</v>
       </c>
-      <c r="Q88">
+      <c r="Q88" s="2">
         <v>20111106</v>
       </c>
-      <c r="R88">
+      <c r="R88" s="2">
         <v>5</v>
       </c>
-      <c r="S88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A89">
+      <c r="S88" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
         <v>14</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="2">
         <v>-96.583299999999994</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="2">
         <v>39.183300000000003</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="2">
         <v>10</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="2">
         <v>11</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="2">
         <v>2012</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="2">
         <v>2007</v>
       </c>
-      <c r="J89">
+      <c r="J89" s="2">
         <v>8</v>
       </c>
-      <c r="K89">
+      <c r="K89" s="2">
         <v>1.098957062</v>
       </c>
-      <c r="N89">
+      <c r="N89" s="2">
         <v>7</v>
       </c>
-      <c r="O89">
+      <c r="O89" s="2">
         <v>10</v>
       </c>
-      <c r="P89">
+      <c r="P89" s="2">
         <v>11</v>
       </c>
-      <c r="Q89">
+      <c r="Q89" s="2">
         <v>20121110</v>
       </c>
-      <c r="R89">
+      <c r="R89" s="2">
         <v>6</v>
       </c>
-      <c r="S89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A90">
+      <c r="S89" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
         <v>14</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="2">
         <v>-96.583299999999994</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="2">
         <v>39.183300000000003</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="2">
         <v>19.100000000000001</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="2">
         <v>8</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="2">
         <v>11</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="2">
         <v>2013</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="2">
         <v>2007</v>
       </c>
-      <c r="J90">
+      <c r="J90" s="2">
         <v>8</v>
       </c>
-      <c r="K90">
+      <c r="K90" s="2">
         <v>1.098957062</v>
       </c>
-      <c r="N90">
+      <c r="N90" s="2">
         <v>7</v>
       </c>
-      <c r="O90">
+      <c r="O90" s="2">
         <v>8</v>
       </c>
-      <c r="P90">
+      <c r="P90" s="2">
         <v>11</v>
       </c>
-      <c r="Q90">
+      <c r="Q90" s="2">
         <v>20131108</v>
       </c>
-      <c r="R90">
+      <c r="R90" s="2">
         <v>7</v>
       </c>
-      <c r="S90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A91">
+      <c r="S90" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
         <v>14</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="2">
         <v>-96.583299999999994</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="2">
         <v>39.183300000000003</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="2">
         <v>20.9</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="2">
         <v>18</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="2">
         <v>11</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="2">
         <v>2014</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="2">
         <v>2007</v>
       </c>
-      <c r="J91">
+      <c r="J91" s="2">
         <v>8</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="2">
         <v>1.098957062</v>
       </c>
-      <c r="N91">
+      <c r="N91" s="2">
         <v>7</v>
       </c>
-      <c r="O91">
+      <c r="O91" s="2">
         <v>18</v>
       </c>
-      <c r="P91">
+      <c r="P91" s="2">
         <v>11</v>
       </c>
-      <c r="Q91">
+      <c r="Q91" s="2">
         <v>20141118</v>
       </c>
-      <c r="R91">
+      <c r="R91" s="2">
         <v>8</v>
       </c>
-      <c r="S91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A92">
+      <c r="S91" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
         <v>14</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="2">
         <v>-96.583299999999994</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="2">
         <v>39.183300000000003</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="2">
         <v>17.5</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="2">
         <v>22</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="2">
         <v>11</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="2">
         <v>2016</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="2">
         <v>2007</v>
       </c>
-      <c r="J92">
+      <c r="J92" s="2">
         <v>8</v>
       </c>
-      <c r="K92">
+      <c r="K92" s="2">
         <v>1.098957062</v>
       </c>
-      <c r="N92">
+      <c r="N92" s="2">
         <v>7</v>
       </c>
-      <c r="O92">
+      <c r="O92" s="2">
         <v>22</v>
       </c>
-      <c r="P92">
+      <c r="P92" s="2">
         <v>11</v>
       </c>
-      <c r="Q92">
+      <c r="Q92" s="2">
         <v>20161122</v>
       </c>
-      <c r="R92">
+      <c r="R92" s="2">
         <v>10</v>
       </c>
-      <c r="S92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A93">
+      <c r="S92" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
         <v>14</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="2">
         <v>-96.583299999999994</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="2">
         <v>39.183300000000003</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="2">
         <v>11.9</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="2">
         <v>21</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="2">
         <v>11</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="2">
         <v>2017</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="2">
         <v>2007</v>
       </c>
-      <c r="J93">
+      <c r="J93" s="2">
         <v>8</v>
       </c>
-      <c r="K93">
+      <c r="K93" s="2">
         <v>1.098957062</v>
       </c>
-      <c r="N93">
+      <c r="N93" s="2">
         <v>7</v>
       </c>
-      <c r="O93">
+      <c r="O93" s="2">
         <v>21</v>
       </c>
-      <c r="P93">
+      <c r="P93" s="2">
         <v>11</v>
       </c>
-      <c r="Q93">
+      <c r="Q93" s="2">
         <v>20171121</v>
       </c>
-      <c r="R93">
+      <c r="R93" s="2">
         <v>11</v>
       </c>
-      <c r="S93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A94">
+      <c r="S93" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
         <v>15</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="1">
         <v>-95.012</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="1">
         <v>42.585999999999999</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="1">
         <v>5.8064</v>
       </c>
-      <c r="E94">
-        <v>4</v>
-      </c>
-      <c r="F94">
-        <v>4</v>
-      </c>
-      <c r="G94">
+      <c r="E94" s="1">
+        <v>4</v>
+      </c>
+      <c r="F94" s="1">
+        <v>4</v>
+      </c>
+      <c r="G94" s="1">
         <v>2016</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="1">
         <v>2015</v>
       </c>
-      <c r="I94" t="s">
+      <c r="I94" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J94">
+      <c r="J94" s="1">
         <v>6</v>
       </c>
-      <c r="K94">
+      <c r="K94" s="1">
         <v>1.4806405309999999</v>
       </c>
-      <c r="L94" t="s">
+      <c r="L94" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N94">
+      <c r="N94" s="1">
         <v>3</v>
       </c>
-      <c r="O94">
-        <v>4</v>
-      </c>
-      <c r="P94">
-        <v>4</v>
-      </c>
-      <c r="Q94">
+      <c r="O94" s="1">
+        <v>4</v>
+      </c>
+      <c r="P94" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="1">
         <v>20160404</v>
       </c>
-      <c r="R94">
-        <v>1</v>
-      </c>
-      <c r="S94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A95">
+      <c r="R94" s="1">
+        <v>1</v>
+      </c>
+      <c r="S94" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
         <v>15</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="1">
         <v>-95.012</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="1">
         <v>42.585999999999999</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="1">
         <v>16.558299999999999</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="1">
         <v>16</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="1">
         <v>2</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="1">
         <v>2017</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="1">
         <v>2015</v>
       </c>
-      <c r="J95">
+      <c r="J95" s="1">
         <v>6</v>
       </c>
-      <c r="K95">
+      <c r="K95" s="1">
         <v>1.4806405309999999</v>
       </c>
-      <c r="N95">
+      <c r="N95" s="1">
         <v>3</v>
       </c>
-      <c r="O95">
+      <c r="O95" s="1">
         <v>16</v>
       </c>
-      <c r="P95">
+      <c r="P95" s="1">
         <v>2</v>
       </c>
-      <c r="Q95">
+      <c r="Q95" s="1">
         <v>20170216</v>
       </c>
-      <c r="R95">
+      <c r="R95" s="1">
         <v>2</v>
       </c>
-      <c r="S95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A96">
+      <c r="S95" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
         <v>15</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="1">
         <v>-95.012</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="1">
         <v>42.585999999999999</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="1">
         <v>20.428599999999999</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="1">
         <v>23</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="1">
         <v>2</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="1">
         <v>2018</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="1">
         <v>2015</v>
       </c>
-      <c r="J96">
+      <c r="J96" s="1">
         <v>6</v>
       </c>
-      <c r="K96">
+      <c r="K96" s="1">
         <v>1.4806405309999999</v>
       </c>
-      <c r="N96">
+      <c r="N96" s="1">
         <v>3</v>
       </c>
-      <c r="O96">
+      <c r="O96" s="1">
         <v>23</v>
       </c>
-      <c r="P96">
+      <c r="P96" s="1">
         <v>2</v>
       </c>
-      <c r="Q96">
+      <c r="Q96" s="1">
         <v>20180223</v>
       </c>
-      <c r="R96">
+      <c r="R96" s="1">
         <v>3</v>
       </c>
-      <c r="S96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A97">
+      <c r="S96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
         <v>16</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="1">
         <v>-93.742999999999995</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="1">
         <v>42.012999999999998</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="1">
         <v>4.3654999999999999</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="1">
         <v>11</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="1">
         <v>3</v>
       </c>
-      <c r="G97">
+      <c r="G97" s="1">
         <v>2016</v>
       </c>
-      <c r="H97">
+      <c r="H97" s="1">
         <v>2015</v>
       </c>
-      <c r="J97">
+      <c r="J97" s="1">
         <v>6</v>
       </c>
-      <c r="K97">
+      <c r="K97" s="1">
         <v>1.500464797</v>
       </c>
-      <c r="N97">
+      <c r="N97" s="1">
         <v>3</v>
       </c>
-      <c r="O97">
+      <c r="O97" s="1">
         <v>11</v>
       </c>
-      <c r="P97">
+      <c r="P97" s="1">
         <v>3</v>
       </c>
-      <c r="Q97">
+      <c r="Q97" s="1">
         <v>20160311</v>
       </c>
-      <c r="R97">
-        <v>1</v>
-      </c>
-      <c r="S97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A98">
+      <c r="R97" s="1">
+        <v>1</v>
+      </c>
+      <c r="S97" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
         <v>16</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="1">
         <v>-93.742999999999995</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="1">
         <v>42.012999999999998</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="1">
         <v>12.958399999999999</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="1">
         <v>23</v>
       </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-      <c r="G98">
+      <c r="F98" s="1">
+        <v>1</v>
+      </c>
+      <c r="G98" s="1">
         <v>2017</v>
       </c>
-      <c r="H98">
+      <c r="H98" s="1">
         <v>2015</v>
       </c>
-      <c r="J98">
+      <c r="J98" s="1">
         <v>6</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="1">
         <v>1.500464797</v>
       </c>
-      <c r="N98">
+      <c r="N98" s="1">
         <v>3</v>
       </c>
-      <c r="O98">
+      <c r="O98" s="1">
         <v>23</v>
       </c>
-      <c r="P98">
-        <v>1</v>
-      </c>
-      <c r="Q98">
+      <c r="P98" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q98" s="1">
         <v>20170123</v>
       </c>
-      <c r="R98">
+      <c r="R98" s="1">
         <v>2</v>
       </c>
-      <c r="S98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A99">
+      <c r="S98" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
         <v>16</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="1">
         <v>-93.742999999999995</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="1">
         <v>42.012999999999998</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="1">
         <v>24.510300000000001</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="1">
         <v>13</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="1">
         <v>2</v>
       </c>
-      <c r="G99">
+      <c r="G99" s="1">
         <v>2018</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="1">
         <v>2015</v>
       </c>
-      <c r="J99">
+      <c r="J99" s="1">
         <v>6</v>
       </c>
-      <c r="K99">
+      <c r="K99" s="1">
         <v>1.500464797</v>
       </c>
-      <c r="N99">
+      <c r="N99" s="1">
         <v>3</v>
       </c>
-      <c r="O99">
+      <c r="O99" s="1">
         <v>13</v>
       </c>
-      <c r="P99">
+      <c r="P99" s="1">
         <v>2</v>
       </c>
-      <c r="Q99">
+      <c r="Q99" s="1">
         <v>20180213</v>
       </c>
-      <c r="R99">
+      <c r="R99" s="1">
         <v>3</v>
       </c>
-      <c r="S99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A100">
+      <c r="S99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
         <v>17</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="1">
         <v>-91.488</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="1">
         <v>41.201000000000001</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="1">
         <v>5.4893000000000001</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="1">
         <v>22</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="1">
         <v>2</v>
       </c>
-      <c r="G100">
+      <c r="G100" s="1">
         <v>2016</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="1">
         <v>2015</v>
       </c>
-      <c r="J100">
+      <c r="J100" s="1">
         <v>8</v>
       </c>
-      <c r="K100">
+      <c r="K100" s="1">
         <v>1.5079703330000001</v>
       </c>
-      <c r="N100">
+      <c r="N100" s="1">
         <v>7</v>
       </c>
-      <c r="O100">
+      <c r="O100" s="1">
         <v>22</v>
       </c>
-      <c r="P100">
+      <c r="P100" s="1">
         <v>2</v>
       </c>
-      <c r="Q100">
+      <c r="Q100" s="1">
         <v>20160222</v>
       </c>
-      <c r="R100">
-        <v>1</v>
-      </c>
-      <c r="S100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A101">
+      <c r="R100" s="1">
+        <v>1</v>
+      </c>
+      <c r="S100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
         <v>17</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="1">
         <v>-91.488</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="1">
         <v>41.201000000000001</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="1">
         <v>17.438199999999998</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="1">
         <v>7</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="1">
         <v>3</v>
       </c>
-      <c r="G101">
+      <c r="G101" s="1">
         <v>2017</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="1">
         <v>2015</v>
       </c>
-      <c r="J101">
+      <c r="J101" s="1">
         <v>8</v>
       </c>
-      <c r="K101">
+      <c r="K101" s="1">
         <v>1.5079703330000001</v>
       </c>
-      <c r="N101">
+      <c r="N101" s="1">
         <v>7</v>
       </c>
-      <c r="O101">
+      <c r="O101" s="1">
         <v>7</v>
       </c>
-      <c r="P101">
+      <c r="P101" s="1">
         <v>3</v>
       </c>
-      <c r="Q101">
+      <c r="Q101" s="1">
         <v>20170307</v>
       </c>
-      <c r="R101">
+      <c r="R101" s="1">
         <v>2</v>
       </c>
-      <c r="S101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A102">
+      <c r="S101" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
         <v>17</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="1">
         <v>-91.488</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="1">
         <v>41.201000000000001</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="1">
         <v>26.670200000000001</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="1">
         <v>9</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="1">
         <v>3</v>
       </c>
-      <c r="G102">
+      <c r="G102" s="1">
         <v>2018</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="1">
         <v>2015</v>
       </c>
-      <c r="J102">
+      <c r="J102" s="1">
         <v>8</v>
       </c>
-      <c r="K102">
+      <c r="K102" s="1">
         <v>1.5079703330000001</v>
       </c>
-      <c r="N102">
+      <c r="N102" s="1">
         <v>7</v>
       </c>
-      <c r="O102">
+      <c r="O102" s="1">
         <v>9</v>
       </c>
-      <c r="P102">
+      <c r="P102" s="1">
         <v>3</v>
       </c>
-      <c r="Q102">
+      <c r="Q102" s="1">
         <v>20180309</v>
       </c>
-      <c r="R102">
+      <c r="R102" s="1">
         <v>3</v>
       </c>
-      <c r="S102">
+      <c r="S102" s="1">
         <v>1</v>
       </c>
     </row>
